--- a/xlsx/final.xlsx
+++ b/xlsx/final.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keith\source\repos\xlladdins\xll_ml\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HW\source\repos\xll_ml\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFEF4C2-697C-475C-BFC8-0C347F24602F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872D7F21-5FBB-4E1A-9741-79EC99914174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$J$5</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$J$6:$J$46</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$K$5</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$K$6:$K$46</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$L$5</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$L$6:$L$46</definedName>
     <definedName name="discrete">Sheet1!$F$2</definedName>
     <definedName name="f">Sheet1!$J$2</definedName>
     <definedName name="k">Sheet1!$J$4</definedName>
@@ -39,9 +45,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -52,6 +55,21 @@
     <author>Keith Lewis</author>
   </authors>
   <commentList>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{41D1B049-24BC-44B5-9D86-A9FF8847899B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Get normalized x's
+Test they have mean 0 and variance 1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{96B00617-888E-49D2-9FA2-33CBF4F0D8F4}">
       <text>
         <r>
@@ -77,21 +95,6 @@
             <family val="2"/>
           </rPr>
           <t>Create discrete distribution from x, p</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{41D1B049-24BC-44B5-9D86-A9FF8847899B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Get normalized x's
-Test they have mean 0 and variance 1</t>
         </r>
       </text>
     </comment>
@@ -150,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>n</t>
   </si>
@@ -184,26 +187,34 @@
   <si>
     <t>strike</t>
   </si>
+  <si>
+    <t>MEAN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARIANCE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;0x&quot;#"/>
+    <numFmt numFmtId="176" formatCode="&quot;0x&quot;#"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color indexed="63"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -213,6 +224,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -234,7 +252,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -246,7 +264,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -333,6 +351,1450 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$K$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>normal_put</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$J$6:$J$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$K$6:$K$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>3.9914343421845189E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7008934088098151E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0058534547871929E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11061799019468133</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15048353300942274</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20168732797265765</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26648097458621844</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34730740212793787</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.44676133725329414</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.56753930674006803</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71238089607367172</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.88400364647703356</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0850344779622993</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3179408286409817</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.5849647756893894</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.8880632480607282</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2288570738163145</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.6085910627585847</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0281066582734937</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.4878279587501879</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.987761167674492</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5275068370385512</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.1062836665495652</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.7229621445706016</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.376105985444056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0640191378988391</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.7847961044341929</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5363734057617648</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.3165802243033653</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.123186539019287</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.953947391857227</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.806642276452777</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.679108988059141</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.569271600088328</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.47516252219144</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.394938837716396</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.326893309710854</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.269460583629098</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.221219204170339</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.180890108309015</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20.14733226325697</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-74F9-4106-8DE6-AFE1BE0C8C4B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$L$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>discrete_put</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$J$6:$J$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$L$6:$L$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>3.4573064104676643E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5267796770692268E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.5962529436707893E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6657262102723518E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1468072231950428</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20446637236496468</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26212552153488655</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.31978467070480843</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.45073969773226352</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.5823276799099979</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71391566208773227</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.84694248217066104</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0986648179860907</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3503871538015204</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.6021094896169501</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.8538318254323798</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2417879786376105</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.6536894526366339</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0655909266356574</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.4774924006346808</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.9772652169830707</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5653637429840472</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.1534622689850238</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.7415607949860004</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.3296593209869769</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0695878701897641</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.8178655343743344</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5661431985589047</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.314420862743475</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.085392292966702</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.953804310788968</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.822216328611233</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.690628346433499</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.559040364255765</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.443145372321311</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.385486223151389</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.327827073981467</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.270167924811545</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.212508775641624</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.155146323373856</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20.13445159070784</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-74F9-4106-8DE6-AFE1BE0C8C4B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1301682496"/>
+        <c:axId val="1301699296"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1301682496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1301699296"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1301699296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1301682496"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>509586</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>126205</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>52386</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>183355</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{201661F4-191A-FDF8-44E2-79AD66B18B4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -652,31 +2114,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9333FE1-19FB-4A1D-86C4-C34A7A2ACCE3}">
-  <dimension ref="B2:N46"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="B1:Z46"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="3.578125" customWidth="1"/>
-    <col min="7" max="7" width="11.68359375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3671875" customWidth="1"/>
+    <col min="1" max="1" width="3.59765625" customWidth="1"/>
+    <col min="3" max="3" width="12.44921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:26" x14ac:dyDescent="0.5">
+      <c r="F1" cm="1">
+        <f t="array" ref="F1:Z1">_xll.OPTION.DISCRETE2(discrete)</f>
+        <v>-4.4721359549995796</v>
+      </c>
+      <c r="G1">
+        <v>-4.0249223594996213</v>
+      </c>
+      <c r="H1">
+        <v>-3.5777087639996634</v>
+      </c>
+      <c r="I1">
+        <v>-3.1304951684997055</v>
+      </c>
+      <c r="J1">
+        <v>-2.6832815729997477</v>
+      </c>
+      <c r="K1">
+        <v>-2.2360679774997898</v>
+      </c>
+      <c r="L1">
+        <v>-1.7888543819998317</v>
+      </c>
+      <c r="M1">
+        <v>-1.3416407864998738</v>
+      </c>
+      <c r="N1">
+        <v>-0.89442719099991586</v>
+      </c>
+      <c r="O1">
+        <v>-0.44721359549995793</v>
+      </c>
+      <c r="P1">
+        <v>0</v>
+      </c>
+      <c r="Q1">
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="R1">
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="S1">
+        <v>1.3416407864998738</v>
+      </c>
+      <c r="T1">
+        <v>1.7888543819998317</v>
+      </c>
+      <c r="U1">
+        <v>2.2360679774997898</v>
+      </c>
+      <c r="V1">
+        <v>2.6832815729997477</v>
+      </c>
+      <c r="W1">
+        <v>3.1304951684997055</v>
+      </c>
+      <c r="X1">
+        <v>3.5777087639996634</v>
+      </c>
+      <c r="Y1">
+        <v>4.0249223594996213</v>
+      </c>
+      <c r="Z1">
+        <v>4.4721359549995796</v>
+      </c>
+    </row>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3" cm="1">
+        <f t="array" ref="F2">_xll.\OPTION.DISCRETE(_xlfn.ANCHORARRAY(D5),_xlfn.ANCHORARRAY(C5))</f>
+        <v>1663252443792</v>
+      </c>
       <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="3" cm="1">
         <f t="array" ref="H2">_xll.\OPTION.NORMAL()</f>
-        <v>1490952485744</v>
+        <v>1662713046432</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>5</v>
@@ -684,16 +2216,30 @@
       <c r="J2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="R2" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2">
+        <f>AVERAGE(_xlfn.ANCHORARRAY(F1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.5">
       <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J3">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="R3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S3">
+        <f>STDEVA(_xlfn.ANCHORARRAY(F1))</f>
+        <v>2.7748873851023217</v>
+      </c>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.5">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -707,17 +2253,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B5" cm="1">
-        <f t="array" ref="B5:B15">_xlfn.SEQUENCE(n+1,1,0)</f>
+        <f t="array" ref="B5:B25">_xlfn.SEQUENCE(n+1,1,0)</f>
         <v>0</v>
       </c>
       <c r="C5" cm="1">
-        <f t="array" ref="C5:C15">_xlfn.BINOM.DIST(_xlfn.ANCHORARRAY(B5),10,0.5,FALSE)</f>
-        <v>9.765625E-4</v>
+        <f t="array" ref="C5:C25">_xlfn.BINOM.DIST(_xlfn.ANCHORARRAY(B5),n,0.5,FALSE)</f>
+        <v>9.5367431640625E-7</v>
       </c>
       <c r="D5" cm="1">
-        <f t="array" ref="D5:D15">_xlfn.ANCHORARRAY(B5)</f>
+        <f t="array" ref="D5:D25">_xlfn.ANCHORARRAY(B5)</f>
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -730,12 +2276,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>9.7656250000000017E-3</v>
+        <v>1.9073486328125034E-5</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -751,13 +2297,17 @@
         <f t="array" ref="K6:K46">_xlfn.MAP(_xlfn.ANCHORARRAY(J6),_xlfn.LAMBDA(_xlpm.k,_xll.OPTION.BLACK.PUT(f,s,_xlpm.k,normal)))</f>
         <v>3.9914343421845189E-2</v>
       </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L6" cm="1">
+        <f t="array" ref="L6:L46">_xlfn.MAP(_xlfn.ANCHORARRAY(J6),_xlfn.LAMBDA(_xlpm.k,_xll.OPTION.BLACK.PUT(f,s,_xlpm.k,discrete)))</f>
+        <v>3.4573064104676643E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>4.3945312499999972E-2</v>
+        <v>1.8119812011718755E-4</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -771,13 +2321,16 @@
       <c r="K7">
         <v>5.7008934088098151E-2</v>
       </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L7">
+        <v>5.5267796770692268E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8">
-        <v>0.11718750000000003</v>
+        <v>1.0871887207031263E-3</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -791,13 +2344,16 @@
       <c r="K8">
         <v>8.0058534547871929E-2</v>
       </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L8">
+        <v>7.5962529436707893E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9">
-        <v>0.20507812500000006</v>
+        <v>4.6205520629882752E-3</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -808,13 +2364,16 @@
       <c r="K9">
         <v>0.11061799019468133</v>
       </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L9">
+        <v>9.6657262102723518E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10">
-        <v>0.24609375000000011</v>
+        <v>1.4785766601562502E-2</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -825,13 +2384,16 @@
       <c r="K10">
         <v>0.15048353300942274</v>
       </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L10">
+        <v>0.1468072231950428</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11">
-        <v>0.20507812500000006</v>
+        <v>3.6964416503906257E-2</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -842,13 +2404,16 @@
       <c r="K11">
         <v>0.20168732797265765</v>
       </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L11">
+        <v>0.20446637236496468</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B12">
         <v>7</v>
       </c>
       <c r="C12">
-        <v>0.11718750000000003</v>
+        <v>7.3928833007812458E-2</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -859,13 +2424,16 @@
       <c r="K12">
         <v>0.26648097458621844</v>
       </c>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L12">
+        <v>0.26212552153488655</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13">
-        <v>4.3945312499999986E-2</v>
+        <v>0.12013435363769531</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -876,13 +2444,16 @@
       <c r="K13">
         <v>0.34730740212793787</v>
       </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L13">
+        <v>0.31978467070480843</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B14">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>9.7656250000000017E-3</v>
+        <v>0.16017913818359369</v>
       </c>
       <c r="D14">
         <v>9</v>
@@ -893,13 +2464,16 @@
       <c r="K14">
         <v>0.44676133725329414</v>
       </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L14">
+        <v>0.45073969773226352</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26" x14ac:dyDescent="0.5">
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15">
-        <v>9.765625E-4</v>
+        <v>0.17619705200195307</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -910,257 +2484,445 @@
       <c r="K15">
         <v>0.56753930674006803</v>
       </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L15">
+        <v>0.5823276799099979</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26" x14ac:dyDescent="0.5">
+      <c r="B16">
+        <v>11</v>
+      </c>
+      <c r="C16">
+        <v>0.16017913818359369</v>
+      </c>
+      <c r="D16">
+        <v>11</v>
+      </c>
       <c r="J16">
         <v>90</v>
       </c>
       <c r="K16">
         <v>0.71238089607367172</v>
       </c>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L16">
+        <v>0.71391566208773227</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.5">
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>0.12013435363769531</v>
+      </c>
+      <c r="D17">
+        <v>12</v>
+      </c>
       <c r="J17">
         <v>91</v>
       </c>
       <c r="K17">
         <v>0.88400364647703356</v>
       </c>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L17">
+        <v>0.84694248217066104</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.5">
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>7.3928833007812472E-2</v>
+      </c>
+      <c r="D18">
+        <v>13</v>
+      </c>
       <c r="J18">
         <v>92</v>
       </c>
       <c r="K18">
         <v>1.0850344779622993</v>
       </c>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L18">
+        <v>1.0986648179860907</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.5">
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19">
+        <v>3.6964416503906257E-2</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
       <c r="J19">
         <v>93</v>
       </c>
       <c r="K19">
         <v>1.3179408286409817</v>
       </c>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L19">
+        <v>1.3503871538015204</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.5">
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20">
+        <v>1.4785766601562502E-2</v>
+      </c>
+      <c r="D20">
+        <v>15</v>
+      </c>
       <c r="J20">
         <v>94</v>
       </c>
       <c r="K20">
         <v>1.5849647756893894</v>
       </c>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L20">
+        <v>1.6021094896169501</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.5">
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <v>4.6205520629882752E-3</v>
+      </c>
+      <c r="D21">
+        <v>16</v>
+      </c>
       <c r="J21">
         <v>95</v>
       </c>
       <c r="K21">
         <v>1.8880632480607282</v>
       </c>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L21">
+        <v>1.8538318254323798</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.5">
+      <c r="B22">
+        <v>17</v>
+      </c>
+      <c r="C22">
+        <v>1.0871887207031261E-3</v>
+      </c>
+      <c r="D22">
+        <v>17</v>
+      </c>
       <c r="J22">
         <v>96</v>
       </c>
       <c r="K22">
         <v>2.2288570738163145</v>
       </c>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L22">
+        <v>2.2417879786376105</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.5">
+      <c r="B23">
+        <v>18</v>
+      </c>
+      <c r="C23">
+        <v>1.8119812011718753E-4</v>
+      </c>
+      <c r="D23">
+        <v>18</v>
+      </c>
       <c r="J23">
         <v>97</v>
       </c>
       <c r="K23">
         <v>2.6085910627585847</v>
       </c>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L23">
+        <v>2.6536894526366339</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.5">
+      <c r="B24">
+        <v>19</v>
+      </c>
+      <c r="C24">
+        <v>1.9073486328125E-5</v>
+      </c>
+      <c r="D24">
+        <v>19</v>
+      </c>
       <c r="J24">
         <v>98</v>
       </c>
       <c r="K24">
         <v>3.0281066582734937</v>
       </c>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L24">
+        <v>3.0655909266356574</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.5">
+      <c r="B25">
+        <v>20</v>
+      </c>
+      <c r="C25">
+        <v>9.5367431640625E-7</v>
+      </c>
+      <c r="D25">
+        <v>20</v>
+      </c>
       <c r="J25">
         <v>99</v>
       </c>
       <c r="K25">
         <v>3.4878279587501879</v>
       </c>
-    </row>
-    <row r="26" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L25">
+        <v>3.4774924006346808</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.5">
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
         <v>3.987761167674492</v>
       </c>
-    </row>
-    <row r="27" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L26">
+        <v>3.9772652169830707</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.5">
       <c r="J27">
         <v>101</v>
       </c>
       <c r="K27">
         <v>4.5275068370385512</v>
       </c>
-    </row>
-    <row r="28" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L27">
+        <v>4.5653637429840472</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.5">
       <c r="J28">
         <v>102</v>
       </c>
       <c r="K28">
         <v>5.1062836665495652</v>
       </c>
-    </row>
-    <row r="29" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L28">
+        <v>5.1534622689850238</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.5">
       <c r="J29">
         <v>103</v>
       </c>
       <c r="K29">
         <v>5.7229621445706016</v>
       </c>
-    </row>
-    <row r="30" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L29">
+        <v>5.7415607949860004</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.5">
       <c r="J30">
         <v>104</v>
       </c>
       <c r="K30">
         <v>6.376105985444056</v>
       </c>
-    </row>
-    <row r="31" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L30">
+        <v>6.3296593209869769</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.5">
       <c r="J31">
         <v>105</v>
       </c>
       <c r="K31">
         <v>7.0640191378988391</v>
       </c>
-    </row>
-    <row r="32" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L31">
+        <v>7.0695878701897641</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.5">
       <c r="J32">
         <v>106</v>
       </c>
       <c r="K32">
         <v>7.7847961044341929</v>
       </c>
-    </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L32">
+        <v>7.8178655343743344</v>
+      </c>
+    </row>
+    <row r="33" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J33">
         <v>107</v>
       </c>
       <c r="K33">
         <v>8.5363734057617648</v>
       </c>
-    </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L33">
+        <v>8.5661431985589047</v>
+      </c>
+    </row>
+    <row r="34" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J34">
         <v>108</v>
       </c>
       <c r="K34">
         <v>9.3165802243033653</v>
       </c>
-    </row>
-    <row r="35" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L34">
+        <v>9.314420862743475</v>
+      </c>
+    </row>
+    <row r="35" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J35">
         <v>109</v>
       </c>
       <c r="K35">
         <v>10.123186539019287</v>
       </c>
-    </row>
-    <row r="36" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L35">
+        <v>10.085392292966702</v>
+      </c>
+    </row>
+    <row r="36" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J36">
         <v>110</v>
       </c>
       <c r="K36">
         <v>10.953947391857227</v>
       </c>
-    </row>
-    <row r="37" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L36">
+        <v>10.953804310788968</v>
+      </c>
+    </row>
+    <row r="37" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J37">
         <v>111</v>
       </c>
       <c r="K37">
         <v>11.806642276452777</v>
       </c>
-    </row>
-    <row r="38" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L37">
+        <v>11.822216328611233</v>
+      </c>
+    </row>
+    <row r="38" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J38">
         <v>112</v>
       </c>
       <c r="K38">
         <v>12.679108988059141</v>
       </c>
-    </row>
-    <row r="39" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L38">
+        <v>12.690628346433499</v>
+      </c>
+    </row>
+    <row r="39" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J39">
         <v>113</v>
       </c>
       <c r="K39">
         <v>13.569271600088328</v>
       </c>
-    </row>
-    <row r="40" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L39">
+        <v>13.559040364255765</v>
+      </c>
+    </row>
+    <row r="40" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J40">
         <v>114</v>
       </c>
       <c r="K40">
         <v>14.47516252219144</v>
       </c>
-    </row>
-    <row r="41" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L40">
+        <v>14.443145372321311</v>
+      </c>
+    </row>
+    <row r="41" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J41">
         <v>115</v>
       </c>
       <c r="K41">
         <v>15.394938837716396</v>
       </c>
-    </row>
-    <row r="42" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L41">
+        <v>15.385486223151389</v>
+      </c>
+    </row>
+    <row r="42" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J42">
         <v>116</v>
       </c>
       <c r="K42">
         <v>16.326893309710854</v>
       </c>
-    </row>
-    <row r="43" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L42">
+        <v>16.327827073981467</v>
+      </c>
+    </row>
+    <row r="43" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J43">
         <v>117</v>
       </c>
       <c r="K43">
         <v>17.269460583629098</v>
       </c>
-    </row>
-    <row r="44" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L43">
+        <v>17.270167924811545</v>
+      </c>
+    </row>
+    <row r="44" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J44">
         <v>118</v>
       </c>
       <c r="K44">
         <v>18.221219204170339</v>
       </c>
-    </row>
-    <row r="45" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L44">
+        <v>18.212508775641624</v>
+      </c>
+    </row>
+    <row r="45" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J45">
         <v>119</v>
       </c>
       <c r="K45">
         <v>19.180890108309015</v>
       </c>
-    </row>
-    <row r="46" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L45">
+        <v>19.155146323373856</v>
+      </c>
+    </row>
+    <row r="46" spans="10:12" x14ac:dyDescent="0.5">
       <c r="J46">
         <v>120</v>
       </c>
       <c r="K46">
         <v>20.14733226325697</v>
       </c>
+      <c r="L46">
+        <v>20.13445159070784</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/xlsx/final.xlsx
+++ b/xlsx/final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keith\source\repos\xlladdins\xll_ml\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81303\OneDrive\桌面\final exam\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFEF4C2-697C-475C-BFC8-0C347F24602F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9C05F5-FB29-47D9-AD6E-9711E12C524B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -150,7 +147,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>n</t>
   </si>
@@ -184,26 +181,50 @@
   <si>
     <t>strike</t>
   </si>
+  <si>
+    <t>mean</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>weighted x</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mean is supposed to be 0, but here it is the machine level episilon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>p*(x-mean)^2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>var</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>So I put mean=0 when calculating the var</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;0x&quot;#"/>
+    <numFmt numFmtId="176" formatCode="&quot;0x&quot;#"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color indexed="63"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -213,6 +234,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -234,7 +262,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -246,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -333,6 +361,1480 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>option</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" baseline="0"/>
+              <a:t> price normal vs discrete</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.25963188976377954"/>
+          <c:y val="5.5555555555555552E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$K$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>normal_put</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$J$6:$J$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$6:$K$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>3.9914343421845189E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7008934088098151E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0058534547871929E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11061799019468133</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15048353300942274</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20168732797265765</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26648097458621844</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34730740212793787</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.44676133725329414</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.56753930674006803</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71238089607367172</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.88400364647703356</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0850344779622993</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3179408286409817</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.5849647756893894</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.8880632480607282</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2288570738163145</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.6085910627585847</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0281066582734937</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.4878279587501879</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.987761167674492</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5275068370385512</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.1062836665495652</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.7229621445706016</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.376105985444056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0640191378988391</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.7847961044341929</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5363734057617648</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.3165802243033653</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.123186539019287</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.953947391857227</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.806642276452777</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.679108988059141</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.569271600088328</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.47516252219144</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.394938837716396</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.326893309710854</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.269460583629098</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.221219204170339</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.180890108309015</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20.14733226325697</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8E3A-42C2-9EE0-D4A2F72B52DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$L$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>discrete_put</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$J$6:$J$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$L$6:$L$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>3.4047379960682855E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4789567460682855E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5531754960682855E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6806891217839919E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15149439121783992</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20618189121783992</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26086939121783992</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.31555689121783992</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40788732068490674</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.57976232068490674</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75163732068490674</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.92351232068490674</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0953873206849067</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2672623206849067</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.561530627262492</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.938483752262492</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.315436877262492</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.692390002262492</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.069343127262492</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.446296252262492</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.9459687470320333</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5690156220320333</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.1920624970320333</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.8151093720320333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.4381562470320333</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0612031220320333</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.6847395769465408</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5128645769465408</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.3409895769465408</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.169114576946541</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.997239576946541</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.825364576946541</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.653489576946541</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.49122085642486</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.43653335642486</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.38184585642486</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.32715835642486</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.27247085642486</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.21778335642486</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.16309585642486</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20.10840835642486</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8E3A-42C2-9EE0-D4A2F72B52DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="126823951"/>
+        <c:axId val="126821071"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="126823951"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="126821071"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="126821071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="126823951"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>163830</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>773430</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB84F009-2661-B44D-000A-B7BAE9274AD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -653,14 +2155,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9333FE1-19FB-4A1D-86C4-C34A7A2ACCE3}">
   <dimension ref="B2:N46"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="3.578125" customWidth="1"/>
-    <col min="7" max="7" width="11.68359375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3671875" customWidth="1"/>
+    <col min="1" max="1" width="3.58203125" customWidth="1"/>
+    <col min="6" max="6" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:14">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -670,13 +2174,16 @@
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3" cm="1">
+        <f t="array" ref="F2">_xll.\OPTION.DISCRETE(_xlfn.ANCHORARRAY(D5),_xlfn.ANCHORARRAY(C5))</f>
+        <v>2740129922784</v>
+      </c>
       <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="3" cm="1">
         <f t="array" ref="H2">_xll.\OPTION.NORMAL()</f>
-        <v>1490952485744</v>
+        <v>2738926692624</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>5</v>
@@ -685,7 +2192,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:14">
+      <c r="F3" cm="1">
+        <f t="array" ref="F3:G13">TRANSPOSE(_xll.OPTION.DISCRETE.NORMALIZED(discrete))</f>
+        <v>-3.1622776601683795</v>
+      </c>
+      <c r="G3">
+        <v>9.765625E-4</v>
+      </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
@@ -693,13 +2207,19 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:14">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="F4">
+        <v>-2.5298221281347035</v>
+      </c>
+      <c r="G4">
+        <v>9.7656250000000017E-3</v>
+      </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
@@ -707,7 +2227,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:14">
       <c r="B5" cm="1">
         <f t="array" ref="B5:B15">_xlfn.SEQUENCE(n+1,1,0)</f>
         <v>0</v>
@@ -720,6 +2240,12 @@
         <f t="array" ref="D5:D15">_xlfn.ANCHORARRAY(B5)</f>
         <v>0</v>
       </c>
+      <c r="F5">
+        <v>-1.8973665961010278</v>
+      </c>
+      <c r="G5">
+        <v>4.3945312499999972E-2</v>
+      </c>
       <c r="J5" s="1" t="s">
         <v>10</v>
       </c>
@@ -730,7 +2256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:14">
       <c r="B6">
         <v>1</v>
       </c>
@@ -739,6 +2265,12 @@
       </c>
       <c r="D6">
         <v>1</v>
+      </c>
+      <c r="F6">
+        <v>-1.2649110640673518</v>
+      </c>
+      <c r="G6">
+        <v>0.11718750000000003</v>
       </c>
       <c r="I6">
         <v>80</v>
@@ -751,8 +2283,12 @@
         <f t="array" ref="K6:K46">_xlfn.MAP(_xlfn.ANCHORARRAY(J6),_xlfn.LAMBDA(_xlpm.k,_xll.OPTION.BLACK.PUT(f,s,_xlpm.k,normal)))</f>
         <v>3.9914343421845189E-2</v>
       </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L6" cm="1">
+        <f t="array" ref="L6">_xll.OPTION.BLACK.PUT(f,s,J6,discrete)</f>
+        <v>3.4047379960682855E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
       <c r="B7">
         <v>2</v>
       </c>
@@ -762,6 +2298,12 @@
       <c r="D7">
         <v>2</v>
       </c>
+      <c r="F7">
+        <v>-0.63245553203367588</v>
+      </c>
+      <c r="G7">
+        <v>0.20507812500000006</v>
+      </c>
       <c r="I7">
         <v>120</v>
       </c>
@@ -771,8 +2313,12 @@
       <c r="K7">
         <v>5.7008934088098151E-2</v>
       </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L7" cm="1">
+        <f t="array" ref="L7">_xll.OPTION.BLACK.PUT(f,s,J7,discrete)</f>
+        <v>4.4789567460682855E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
       <c r="B8">
         <v>3</v>
       </c>
@@ -782,6 +2328,12 @@
       <c r="D8">
         <v>3</v>
       </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0.24609375000000011</v>
+      </c>
       <c r="I8">
         <v>1</v>
       </c>
@@ -791,8 +2343,12 @@
       <c r="K8">
         <v>8.0058534547871929E-2</v>
       </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L8" cm="1">
+        <f t="array" ref="L8">_xll.OPTION.BLACK.PUT(f,s,J8,discrete)</f>
+        <v>5.5531754960682855E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
       <c r="B9">
         <v>4</v>
       </c>
@@ -802,14 +2358,24 @@
       <c r="D9">
         <v>4</v>
       </c>
+      <c r="F9">
+        <v>0.63245553203367588</v>
+      </c>
+      <c r="G9">
+        <v>0.20507812500000006</v>
+      </c>
       <c r="J9">
         <v>83</v>
       </c>
       <c r="K9">
         <v>0.11061799019468133</v>
       </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L9" cm="1">
+        <f t="array" ref="L9">_xll.OPTION.BLACK.PUT(f,s,J9,discrete)</f>
+        <v>9.6806891217839919E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
       <c r="B10">
         <v>5</v>
       </c>
@@ -819,14 +2385,24 @@
       <c r="D10">
         <v>5</v>
       </c>
+      <c r="F10">
+        <v>1.2649110640673518</v>
+      </c>
+      <c r="G10">
+        <v>0.11718750000000003</v>
+      </c>
       <c r="J10">
         <v>84</v>
       </c>
       <c r="K10">
         <v>0.15048353300942274</v>
       </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L10" cm="1">
+        <f t="array" ref="L10">_xll.OPTION.BLACK.PUT(f,s,J10,discrete)</f>
+        <v>0.15149439121783992</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
       <c r="B11">
         <v>6</v>
       </c>
@@ -836,14 +2412,24 @@
       <c r="D11">
         <v>6</v>
       </c>
+      <c r="F11">
+        <v>1.8973665961010278</v>
+      </c>
+      <c r="G11">
+        <v>4.3945312499999986E-2</v>
+      </c>
       <c r="J11">
         <v>85</v>
       </c>
       <c r="K11">
         <v>0.20168732797265765</v>
       </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L11" cm="1">
+        <f t="array" ref="L11">_xll.OPTION.BLACK.PUT(f,s,J11,discrete)</f>
+        <v>0.20618189121783992</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
       <c r="B12">
         <v>7</v>
       </c>
@@ -853,14 +2439,24 @@
       <c r="D12">
         <v>7</v>
       </c>
+      <c r="F12">
+        <v>2.5298221281347035</v>
+      </c>
+      <c r="G12">
+        <v>9.7656250000000017E-3</v>
+      </c>
       <c r="J12">
         <v>86</v>
       </c>
       <c r="K12">
         <v>0.26648097458621844</v>
       </c>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L12" cm="1">
+        <f t="array" ref="L12">_xll.OPTION.BLACK.PUT(f,s,J12,discrete)</f>
+        <v>0.26086939121783992</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
       <c r="B13">
         <v>8</v>
       </c>
@@ -870,14 +2466,24 @@
       <c r="D13">
         <v>8</v>
       </c>
+      <c r="F13">
+        <v>3.1622776601683795</v>
+      </c>
+      <c r="G13">
+        <v>9.765625E-4</v>
+      </c>
       <c r="J13">
         <v>87</v>
       </c>
       <c r="K13">
         <v>0.34730740212793787</v>
       </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L13" cm="1">
+        <f t="array" ref="L13">_xll.OPTION.BLACK.PUT(f,s,J13,discrete)</f>
+        <v>0.31555689121783992</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
       <c r="B14">
         <v>9</v>
       </c>
@@ -893,8 +2499,12 @@
       <c r="K14">
         <v>0.44676133725329414</v>
       </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L14" cm="1">
+        <f t="array" ref="L14">_xll.OPTION.BLACK.PUT(f,s,J14,discrete)</f>
+        <v>0.40788732068490674</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
       <c r="B15">
         <v>10</v>
       </c>
@@ -910,257 +2520,501 @@
       <c r="K15">
         <v>0.56753930674006803</v>
       </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L15" cm="1">
+        <f t="array" ref="L15">_xll.OPTION.BLACK.PUT(f,s,J15,discrete)</f>
+        <v>0.57976232068490674</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
       <c r="J16">
         <v>90</v>
       </c>
       <c r="K16">
         <v>0.71238089607367172</v>
       </c>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L16" cm="1">
+        <f t="array" ref="L16">_xll.OPTION.BLACK.PUT(f,s,J16,discrete)</f>
+        <v>0.75163732068490674</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12">
+      <c r="F17">
+        <f>F3*G3</f>
+        <v>-3.0881617775081831E-3</v>
+      </c>
+      <c r="G17">
+        <f>G3*F3^2</f>
+        <v>9.7656250000000017E-3</v>
+      </c>
       <c r="J17">
         <v>91</v>
       </c>
       <c r="K17">
         <v>0.88400364647703356</v>
       </c>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L17" cm="1">
+        <f t="array" ref="L17">_xll.OPTION.BLACK.PUT(f,s,J17,discrete)</f>
+        <v>0.92351232068490674</v>
+      </c>
+    </row>
+    <row r="18" spans="5:12">
+      <c r="F18">
+        <f t="shared" ref="F18:F27" si="0">F4*G4</f>
+        <v>-2.4705294220065468E-2</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18:G27" si="1">G4*F4^2</f>
+        <v>6.2500000000000014E-2</v>
+      </c>
       <c r="J18">
         <v>92</v>
       </c>
       <c r="K18">
         <v>1.0850344779622993</v>
       </c>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L18" cm="1">
+        <f t="array" ref="L18">_xll.OPTION.BLACK.PUT(f,s,J18,discrete)</f>
+        <v>1.0953873206849067</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12">
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>-8.3380367992720889E-2</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="1"/>
+        <v>0.15820312499999992</v>
+      </c>
       <c r="J19">
         <v>93</v>
       </c>
       <c r="K19">
         <v>1.3179408286409817</v>
       </c>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L19" cm="1">
+        <f t="array" ref="L19">_xll.OPTION.BLACK.PUT(f,s,J19,discrete)</f>
+        <v>1.2672623206849067</v>
+      </c>
+    </row>
+    <row r="20" spans="5:12">
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>-0.14823176532039281</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="1"/>
+        <v>0.18750000000000006</v>
+      </c>
       <c r="J20">
         <v>94</v>
       </c>
       <c r="K20">
         <v>1.5849647756893894</v>
       </c>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L20" cm="1">
+        <f t="array" ref="L20">_xll.OPTION.BLACK.PUT(f,s,J20,discrete)</f>
+        <v>1.561530627262492</v>
+      </c>
+    </row>
+    <row r="21" spans="5:12">
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>-0.12970279465534373</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="1"/>
+        <v>8.2031250000000028E-2</v>
+      </c>
       <c r="J21">
         <v>95</v>
       </c>
       <c r="K21">
         <v>1.8880632480607282</v>
       </c>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L21" cm="1">
+        <f t="array" ref="L21">_xll.OPTION.BLACK.PUT(f,s,J21,discrete)</f>
+        <v>1.938483752262492</v>
+      </c>
+    </row>
+    <row r="22" spans="5:12">
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="J22">
         <v>96</v>
       </c>
       <c r="K22">
         <v>2.2288570738163145</v>
       </c>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L22" cm="1">
+        <f t="array" ref="L22">_xll.OPTION.BLACK.PUT(f,s,J22,discrete)</f>
+        <v>2.315436877262492</v>
+      </c>
+    </row>
+    <row r="23" spans="5:12">
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>0.12970279465534373</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>8.2031250000000028E-2</v>
+      </c>
       <c r="J23">
         <v>97</v>
       </c>
       <c r="K23">
         <v>2.6085910627585847</v>
       </c>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L23" cm="1">
+        <f t="array" ref="L23">_xll.OPTION.BLACK.PUT(f,s,J23,discrete)</f>
+        <v>2.692390002262492</v>
+      </c>
+    </row>
+    <row r="24" spans="5:12">
+      <c r="F24">
+        <f>F10*G10</f>
+        <v>0.14823176532039281</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>0.18750000000000006</v>
+      </c>
       <c r="J24">
         <v>98</v>
       </c>
       <c r="K24">
         <v>3.0281066582734937</v>
       </c>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L24" cm="1">
+        <f t="array" ref="L24">_xll.OPTION.BLACK.PUT(f,s,J24,discrete)</f>
+        <v>3.069343127262492</v>
+      </c>
+    </row>
+    <row r="25" spans="5:12">
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>8.3380367992720916E-2</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="1"/>
+        <v>0.15820312499999997</v>
+      </c>
       <c r="J25">
         <v>99</v>
       </c>
       <c r="K25">
         <v>3.4878279587501879</v>
       </c>
-    </row>
-    <row r="26" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L25" cm="1">
+        <f t="array" ref="L25">_xll.OPTION.BLACK.PUT(f,s,J25,discrete)</f>
+        <v>3.446296252262492</v>
+      </c>
+    </row>
+    <row r="26" spans="5:12">
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>2.4705294220065468E-2</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="1"/>
+        <v>6.2500000000000014E-2</v>
+      </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
         <v>3.987761167674492</v>
       </c>
-    </row>
-    <row r="27" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L26" cm="1">
+        <f t="array" ref="L26">_xll.OPTION.BLACK.PUT(f,s,J26,discrete)</f>
+        <v>3.9459687470320333</v>
+      </c>
+    </row>
+    <row r="27" spans="5:12">
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>3.0881617775081831E-3</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="1"/>
+        <v>9.7656250000000017E-3</v>
+      </c>
       <c r="J27">
         <v>101</v>
       </c>
       <c r="K27">
         <v>4.5275068370385512</v>
       </c>
-    </row>
-    <row r="28" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L27" cm="1">
+        <f t="array" ref="L27">_xll.OPTION.BLACK.PUT(f,s,J27,discrete)</f>
+        <v>4.5690156220320333</v>
+      </c>
+    </row>
+    <row r="28" spans="5:12">
       <c r="J28">
         <v>102</v>
       </c>
       <c r="K28">
         <v>5.1062836665495652</v>
       </c>
-    </row>
-    <row r="29" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L28" cm="1">
+        <f t="array" ref="L28">_xll.OPTION.BLACK.PUT(f,s,J28,discrete)</f>
+        <v>5.1920624970320333</v>
+      </c>
+    </row>
+    <row r="29" spans="5:12">
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" t="s">
+        <v>15</v>
+      </c>
       <c r="J29">
         <v>103</v>
       </c>
       <c r="K29">
         <v>5.7229621445706016</v>
       </c>
-    </row>
-    <row r="30" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L29" cm="1">
+        <f t="array" ref="L29">_xll.OPTION.BLACK.PUT(f,s,J29,discrete)</f>
+        <v>5.8151093720320333</v>
+      </c>
+    </row>
+    <row r="30" spans="5:12">
+      <c r="F30">
+        <f>SUM(F17:F27)</f>
+        <v>2.211772431870429E-17</v>
+      </c>
+      <c r="G30">
+        <f>SUM(G17:G27)</f>
+        <v>1</v>
+      </c>
       <c r="J30">
         <v>104</v>
       </c>
       <c r="K30">
         <v>6.376105985444056</v>
       </c>
-    </row>
-    <row r="31" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L30" cm="1">
+        <f t="array" ref="L30">_xll.OPTION.BLACK.PUT(f,s,J30,discrete)</f>
+        <v>6.4381562470320333</v>
+      </c>
+    </row>
+    <row r="31" spans="5:12">
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
       <c r="J31">
         <v>105</v>
       </c>
       <c r="K31">
         <v>7.0640191378988391</v>
       </c>
-    </row>
-    <row r="32" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L31" cm="1">
+        <f t="array" ref="L31">_xll.OPTION.BLACK.PUT(f,s,J31,discrete)</f>
+        <v>7.0612031220320333</v>
+      </c>
+    </row>
+    <row r="32" spans="5:12">
+      <c r="E32" t="s">
+        <v>16</v>
+      </c>
       <c r="J32">
         <v>106</v>
       </c>
       <c r="K32">
         <v>7.7847961044341929</v>
       </c>
-    </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L32" cm="1">
+        <f t="array" ref="L32">_xll.OPTION.BLACK.PUT(f,s,J32,discrete)</f>
+        <v>7.6847395769465408</v>
+      </c>
+    </row>
+    <row r="33" spans="10:12">
       <c r="J33">
         <v>107</v>
       </c>
       <c r="K33">
         <v>8.5363734057617648</v>
       </c>
-    </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L33" cm="1">
+        <f t="array" ref="L33">_xll.OPTION.BLACK.PUT(f,s,J33,discrete)</f>
+        <v>8.5128645769465408</v>
+      </c>
+    </row>
+    <row r="34" spans="10:12">
       <c r="J34">
         <v>108</v>
       </c>
       <c r="K34">
         <v>9.3165802243033653</v>
       </c>
-    </row>
-    <row r="35" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L34" cm="1">
+        <f t="array" ref="L34">_xll.OPTION.BLACK.PUT(f,s,J34,discrete)</f>
+        <v>9.3409895769465408</v>
+      </c>
+    </row>
+    <row r="35" spans="10:12">
       <c r="J35">
         <v>109</v>
       </c>
       <c r="K35">
         <v>10.123186539019287</v>
       </c>
-    </row>
-    <row r="36" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L35" cm="1">
+        <f t="array" ref="L35">_xll.OPTION.BLACK.PUT(f,s,J35,discrete)</f>
+        <v>10.169114576946541</v>
+      </c>
+    </row>
+    <row r="36" spans="10:12">
       <c r="J36">
         <v>110</v>
       </c>
       <c r="K36">
         <v>10.953947391857227</v>
       </c>
-    </row>
-    <row r="37" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L36" cm="1">
+        <f t="array" ref="L36">_xll.OPTION.BLACK.PUT(f,s,J36,discrete)</f>
+        <v>10.997239576946541</v>
+      </c>
+    </row>
+    <row r="37" spans="10:12">
       <c r="J37">
         <v>111</v>
       </c>
       <c r="K37">
         <v>11.806642276452777</v>
       </c>
-    </row>
-    <row r="38" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L37" cm="1">
+        <f t="array" ref="L37">_xll.OPTION.BLACK.PUT(f,s,J37,discrete)</f>
+        <v>11.825364576946541</v>
+      </c>
+    </row>
+    <row r="38" spans="10:12">
       <c r="J38">
         <v>112</v>
       </c>
       <c r="K38">
         <v>12.679108988059141</v>
       </c>
-    </row>
-    <row r="39" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L38" cm="1">
+        <f t="array" ref="L38">_xll.OPTION.BLACK.PUT(f,s,J38,discrete)</f>
+        <v>12.653489576946541</v>
+      </c>
+    </row>
+    <row r="39" spans="10:12">
       <c r="J39">
         <v>113</v>
       </c>
       <c r="K39">
         <v>13.569271600088328</v>
       </c>
-    </row>
-    <row r="40" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L39" cm="1">
+        <f t="array" ref="L39">_xll.OPTION.BLACK.PUT(f,s,J39,discrete)</f>
+        <v>13.49122085642486</v>
+      </c>
+    </row>
+    <row r="40" spans="10:12">
       <c r="J40">
         <v>114</v>
       </c>
       <c r="K40">
         <v>14.47516252219144</v>
       </c>
-    </row>
-    <row r="41" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L40" cm="1">
+        <f t="array" ref="L40">_xll.OPTION.BLACK.PUT(f,s,J40,discrete)</f>
+        <v>14.43653335642486</v>
+      </c>
+    </row>
+    <row r="41" spans="10:12">
       <c r="J41">
         <v>115</v>
       </c>
       <c r="K41">
         <v>15.394938837716396</v>
       </c>
-    </row>
-    <row r="42" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L41" cm="1">
+        <f t="array" ref="L41">_xll.OPTION.BLACK.PUT(f,s,J41,discrete)</f>
+        <v>15.38184585642486</v>
+      </c>
+    </row>
+    <row r="42" spans="10:12">
       <c r="J42">
         <v>116</v>
       </c>
       <c r="K42">
         <v>16.326893309710854</v>
       </c>
-    </row>
-    <row r="43" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L42" cm="1">
+        <f t="array" ref="L42">_xll.OPTION.BLACK.PUT(f,s,J42,discrete)</f>
+        <v>16.32715835642486</v>
+      </c>
+    </row>
+    <row r="43" spans="10:12">
       <c r="J43">
         <v>117</v>
       </c>
       <c r="K43">
         <v>17.269460583629098</v>
       </c>
-    </row>
-    <row r="44" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L43" cm="1">
+        <f t="array" ref="L43">_xll.OPTION.BLACK.PUT(f,s,J43,discrete)</f>
+        <v>17.27247085642486</v>
+      </c>
+    </row>
+    <row r="44" spans="10:12">
       <c r="J44">
         <v>118</v>
       </c>
       <c r="K44">
         <v>18.221219204170339</v>
       </c>
-    </row>
-    <row r="45" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L44" cm="1">
+        <f t="array" ref="L44">_xll.OPTION.BLACK.PUT(f,s,J44,discrete)</f>
+        <v>18.21778335642486</v>
+      </c>
+    </row>
+    <row r="45" spans="10:12">
       <c r="J45">
         <v>119</v>
       </c>
       <c r="K45">
         <v>19.180890108309015</v>
       </c>
-    </row>
-    <row r="46" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L45" cm="1">
+        <f t="array" ref="L45">_xll.OPTION.BLACK.PUT(f,s,J45,discrete)</f>
+        <v>19.16309585642486</v>
+      </c>
+    </row>
+    <row r="46" spans="10:12">
       <c r="J46">
         <v>120</v>
       </c>
       <c r="K46">
         <v>20.14733226325697</v>
       </c>
+      <c r="L46" cm="1">
+        <f t="array" ref="L46">_xll.OPTION.BLACK.PUT(f,s,J46,discrete)</f>
+        <v>20.10840835642486</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/xlsx/final.xlsx
+++ b/xlsx/final.xlsx
@@ -5,17 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adithyah Nair\source\repos\xll_ml\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gokul\source\repos\xll_ml_god\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE54975-D4BE-4156-B739-68ECA8F4D015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412D8ABF-CA2F-4DFE-ADD7-91086212C9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22290" windowHeight="13305" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$J$6:$J$46</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$K$5</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$K$6:$K$46</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$L$5</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$L$6:$L$46</definedName>
     <definedName name="discrete">Sheet1!$F$2</definedName>
     <definedName name="f">Sheet1!$J$2</definedName>
     <definedName name="k">Sheet1!$J$4</definedName>
@@ -126,9 +131,8 @@
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
+  <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -139,35 +143,11 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-    <bk>
-      <rc t="2" v="1"/>
-    </bk>
-  </valueMetadata>
 </metadata>
 </file>
 
@@ -392,7 +372,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Strike vs Put values</a:t>
+              <a:t>Normal vs Discrete Put Prices</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -429,8 +409,9 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -447,17 +428,15 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
               <c:f>Sheet1!$J$6:$J$46</c:f>
@@ -722,7 +701,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-406F-4560-B385-0401BE3EFE52}"/>
@@ -744,17 +722,15 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
               <c:f>Sheet1!$J$6:$J$46</c:f>
@@ -1019,7 +995,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-406F-4560-B385-0401BE3EFE52}"/>
@@ -1034,10 +1009,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
+        <c:gapWidth val="150"/>
         <c:axId val="1214146496"/>
         <c:axId val="1214164736"/>
-      </c:lineChart>
+      </c:barChart>
       <c:catAx>
         <c:axId val="1214146496"/>
         <c:scaling>
@@ -1781,15 +1756,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>23812</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>14287</xdr:colOff>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>404812</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>633412</xdr:colOff>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1816,76 +1791,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
-  <rv s="0">
-    <v>10</v>
-    <v>8</v>
-    <v>0</v>
-    <v>1</v>
-  </rv>
-  <rv s="1">
-    <v>8</v>
-    <v>1</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
-  <s t="_error">
-    <k n="colOffset" t="i"/>
-    <k n="errorType" t="i"/>
-    <k n="rwOffset" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="propagated" t="b"/>
-  </s>
-</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2243,9 +2148,9 @@
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="F3" t="e" cm="1" vm="1">
+      <c r="F3" t="e" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">_xll.OPTION.DISCRETE.XI(F2)</f>
-        <v>#VALUE!</v>
+        <v>#NAME?</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
@@ -2845,9 +2750,9 @@
       </c>
     </row>
     <row r="216" spans="15:15" x14ac:dyDescent="0.3">
-      <c r="O216" t="e" vm="2">
+      <c r="O216" t="e">
         <f ca="1">AVERAGE(_xlfn.ANCHORARRAY(F3))</f>
-        <v>#VALUE!</v>
+        <v>#NAME?</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/final.xlsx
+++ b/xlsx/final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keith\source\repos\xlladdins\xll_ml\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikhildonde\exm\xll_ml\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFEF4C2-697C-475C-BFC8-0C347F24602F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB895AD-6D3A-4ECC-9BDE-1B3F632A05A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12030" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="normal">Sheet1!$H$2</definedName>
     <definedName name="s">Sheet1!$J$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,9 +38,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -182,7 +179,7 @@
     <t>discrete_put</t>
   </si>
   <si>
-    <t>strike</t>
+    <t xml:space="preserve">strike, </t>
   </si>
 </sst>
 </file>
@@ -333,6 +330,2813 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Line</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Grpah: Put Value vs Strike</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.2016404199475071E-2"/>
+          <c:y val="0.1902314814814815"/>
+          <c:w val="0.88949759405074369"/>
+          <c:h val="0.6153546952464275"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$N$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>strike, </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$7:$N$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F5EA-452A-A55E-036E886AE6B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$O$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>normal_put</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$O$7:$O$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>3.9914343421845189E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7008934088089269E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0058534547881699E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11061799019469776</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15048353300942274</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20168732797265232</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.266480974586214</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34730740212793254</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.44676133725329414</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.56753930674006803</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71238089607367172</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.8840036464770229</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0850344779622993</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3179408286409817</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.5849647756893894</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.8880632480607282</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2288570738163145</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.6085910627585847</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0281066582734937</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.4878279587501879</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.987761167674492</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5275068370385512</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.1062836665495652</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.7229621445706016</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.376105985444056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0640191378988391</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.7847961044341929</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5363734057617648</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.3165802243033653</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.123186539019301</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.953947391857241</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.806642276452777</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.679108988059141</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.569271600088314</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.47516252219144</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.394938837716396</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.326893309710854</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.269460583629098</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.221219204170353</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.180890108309015</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20.14733226325697</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-F5EA-452A-A55E-036E886AE6B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$P$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>discrete_put</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$P$7:$P$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>3.4047379960682522E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4789567460682522E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5531754960682522E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6806891217839031E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15149439121783903</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20618189121783903</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26086939121783903</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.31555689121783903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40788732068490319</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.57976232068490319</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75163732068490319</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.92351232068490319</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0953873206849032</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2672623206849032</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.561530627262492</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.938483752262492</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.315436877262492</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.692390002262492</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.069343127262492</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.446296252262492</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.9459687470320333</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5690156220320333</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.1920624970320333</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.8151093720320333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.4381562470320333</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0612031220320333</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.6847395769465408</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5128645769465408</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.3409895769465408</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.169114576946541</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.997239576946541</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.825364576946541</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.653489576946541</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.49122085642486</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.43653335642486</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.38184585642486</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.32715835642486</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.27247085642486</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.21778335642486</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.16309585642486</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20.10840835642486</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-F5EA-452A-A55E-036E886AE6B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="741855935"/>
+        <c:axId val="741856415"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="741855935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="741856415"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="741856415"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="741855935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Stacked</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Line Graph : Put price vs Strike</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.993545921736223E-2"/>
+          <c:y val="0.10333741769743317"/>
+          <c:w val="0.94967352294571539"/>
+          <c:h val="0.86784257776104456"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$N$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>strike, </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$7:$N$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DBB4-4A14-BADE-EC29400C6DA4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$O$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>normal_put</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$O$7:$O$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>3.9914343421845189E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7008934088089269E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0058534547881699E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11061799019469776</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15048353300942274</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20168732797265232</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.266480974586214</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34730740212793254</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.44676133725329414</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.56753930674006803</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71238089607367172</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.8840036464770229</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0850344779622993</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3179408286409817</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.5849647756893894</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.8880632480607282</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2288570738163145</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.6085910627585847</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0281066582734937</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.4878279587501879</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.987761167674492</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5275068370385512</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.1062836665495652</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.7229621445706016</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.376105985444056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0640191378988391</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.7847961044341929</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5363734057617648</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.3165802243033653</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.123186539019301</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.953947391857241</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.806642276452777</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.679108988059141</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.569271600088314</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.47516252219144</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.394938837716396</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.326893309710854</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.269460583629098</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.221219204170353</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.180890108309015</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20.14733226325697</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DBB4-4A14-BADE-EC29400C6DA4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$P$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>discrete_put</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$P$7:$P$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>3.4047379960682522E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4789567460682522E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5531754960682522E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6806891217839031E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15149439121783903</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20618189121783903</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26086939121783903</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.31555689121783903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40788732068490319</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.57976232068490319</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75163732068490319</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.92351232068490319</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0953873206849032</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2672623206849032</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.561530627262492</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.938483752262492</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.315436877262492</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.692390002262492</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.069343127262492</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.446296252262492</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.9459687470320333</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5690156220320333</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.1920624970320333</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.8151093720320333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.4381562470320333</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0612031220320333</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.6847395769465408</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5128645769465408</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.3409895769465408</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.169114576946541</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.997239576946541</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.825364576946541</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.653489576946541</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.49122085642486</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.43653335642486</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.38184585642486</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.32715835642486</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.27247085642486</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.21778335642486</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.16309585642486</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20.10840835642486</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DBB4-4A14-BADE-EC29400C6DA4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1522165936"/>
+        <c:axId val="1522164496"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1522165936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1522164496"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1522164496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1522165936"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>765908</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>188702</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>107829</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>71886</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DB3442B-7D21-E6B1-38BB-0F7CD2462339}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>781901</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>431319</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>188702</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{098A98AD-83E6-8A02-30ED-37871F99A8DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -652,15 +3456,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9333FE1-19FB-4A1D-86C4-C34A7A2ACCE3}">
-  <dimension ref="B2:N46"/>
+  <dimension ref="B2:P47"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.578125" customWidth="1"/>
+    <col min="6" max="6" width="9.05078125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.68359375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.3671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -670,13 +3475,16 @@
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3">
+        <f>_xll.\OPTION.DISCRETE(_xlfn.ANCHORARRAY(D5),_xlfn.ANCHORARRAY( C5))</f>
+        <v>2838710486032</v>
+      </c>
       <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="3" cm="1">
         <f t="array" ref="H2">_xll.\OPTION.NORMAL()</f>
-        <v>1490952485744</v>
+        <v>2837174627440</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>5</v>
@@ -685,7 +3493,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="F3" cm="1">
+        <f t="array" ref="F3:F13">_xll.OPTION.DISCRETE(discrete)</f>
+        <v>-3.1622776601683795</v>
+      </c>
+      <c r="G3">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(F3),_xlfn.ANCHORARRAY(C5))/SUM(_xlfn.ANCHORARRAY(C5))</f>
+        <v>2.2117724318704284E-17</v>
+      </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
@@ -693,13 +3509,20 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="F4">
+        <v>-2.5298221281347035</v>
+      </c>
+      <c r="G4" cm="1">
+        <f t="array" ref="G4">SUMPRODUCT(_xlfn.ANCHORARRAY(F3)*_xlfn.ANCHORARRAY(F3),_xlfn.ANCHORARRAY(C5))/SUM(_xlfn.ANCHORARRAY(C5))</f>
+        <v>0.99999999999999978</v>
+      </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
@@ -707,7 +3530,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" cm="1">
         <f t="array" ref="B5:B15">_xlfn.SEQUENCE(n+1,1,0)</f>
         <v>0</v>
@@ -720,6 +3543,9 @@
         <f t="array" ref="D5:D15">_xlfn.ANCHORARRAY(B5)</f>
         <v>0</v>
       </c>
+      <c r="F5">
+        <v>-1.8973665961010278</v>
+      </c>
       <c r="J5" s="1" t="s">
         <v>10</v>
       </c>
@@ -730,7 +3556,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B6">
         <v>1</v>
       </c>
@@ -739,6 +3565,9 @@
       </c>
       <c r="D6">
         <v>1</v>
+      </c>
+      <c r="F6">
+        <v>-1.2649110640673518</v>
       </c>
       <c r="I6">
         <v>80</v>
@@ -751,8 +3580,22 @@
         <f t="array" ref="K6:K46">_xlfn.MAP(_xlfn.ANCHORARRAY(J6),_xlfn.LAMBDA(_xlpm.k,_xll.OPTION.BLACK.PUT(f,s,_xlpm.k,normal)))</f>
         <v>3.9914343421845189E-2</v>
       </c>
+      <c r="L6" cm="1">
+        <f t="array" ref="L6:L46">_xlfn.MAP(_xlfn.ANCHORARRAY(J6),_xlfn.LAMBDA(_xlpm.k,_xll.OPTION.BLACK.PUT(f,s,_xlpm.k,discrete)))</f>
+        <v>3.4047379960682522E-2</v>
+      </c>
+      <c r="N6" t="str" cm="1">
+        <f t="array" ref="N6:P47">J5:L46</f>
+        <v xml:space="preserve">strike, </v>
+      </c>
+      <c r="O6" t="str">
+        <v>normal_put</v>
+      </c>
+      <c r="P6" t="str">
+        <v>discrete_put</v>
+      </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7">
         <v>2</v>
       </c>
@@ -762,6 +3605,9 @@
       <c r="D7">
         <v>2</v>
       </c>
+      <c r="F7">
+        <v>-0.63245553203367588</v>
+      </c>
       <c r="I7">
         <v>120</v>
       </c>
@@ -769,10 +3615,22 @@
         <v>81</v>
       </c>
       <c r="K7">
-        <v>5.7008934088098151E-2</v>
+        <v>5.7008934088089269E-2</v>
+      </c>
+      <c r="L7">
+        <v>4.4789567460682522E-2</v>
+      </c>
+      <c r="N7">
+        <v>80</v>
+      </c>
+      <c r="O7">
+        <v>3.9914343421845189E-2</v>
+      </c>
+      <c r="P7">
+        <v>3.4047379960682522E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B8">
         <v>3</v>
       </c>
@@ -782,6 +3640,9 @@
       <c r="D8">
         <v>3</v>
       </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
       <c r="I8">
         <v>1</v>
       </c>
@@ -789,10 +3650,22 @@
         <v>82</v>
       </c>
       <c r="K8">
-        <v>8.0058534547871929E-2</v>
+        <v>8.0058534547881699E-2</v>
+      </c>
+      <c r="L8">
+        <v>5.5531754960682522E-2</v>
+      </c>
+      <c r="N8">
+        <v>81</v>
+      </c>
+      <c r="O8">
+        <v>5.7008934088089269E-2</v>
+      </c>
+      <c r="P8">
+        <v>4.4789567460682522E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B9">
         <v>4</v>
       </c>
@@ -802,14 +3675,29 @@
       <c r="D9">
         <v>4</v>
       </c>
+      <c r="F9">
+        <v>0.63245553203367588</v>
+      </c>
       <c r="J9">
         <v>83</v>
       </c>
       <c r="K9">
-        <v>0.11061799019468133</v>
+        <v>0.11061799019469776</v>
+      </c>
+      <c r="L9">
+        <v>9.6806891217839031E-2</v>
+      </c>
+      <c r="N9">
+        <v>82</v>
+      </c>
+      <c r="O9">
+        <v>8.0058534547881699E-2</v>
+      </c>
+      <c r="P9">
+        <v>5.5531754960682522E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B10">
         <v>5</v>
       </c>
@@ -819,14 +3707,29 @@
       <c r="D10">
         <v>5</v>
       </c>
+      <c r="F10">
+        <v>1.2649110640673518</v>
+      </c>
       <c r="J10">
         <v>84</v>
       </c>
       <c r="K10">
         <v>0.15048353300942274</v>
       </c>
+      <c r="L10">
+        <v>0.15149439121783903</v>
+      </c>
+      <c r="N10">
+        <v>83</v>
+      </c>
+      <c r="O10">
+        <v>0.11061799019469776</v>
+      </c>
+      <c r="P10">
+        <v>9.6806891217839031E-2</v>
+      </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B11">
         <v>6</v>
       </c>
@@ -836,14 +3739,29 @@
       <c r="D11">
         <v>6</v>
       </c>
+      <c r="F11">
+        <v>1.8973665961010278</v>
+      </c>
       <c r="J11">
         <v>85</v>
       </c>
       <c r="K11">
-        <v>0.20168732797265765</v>
+        <v>0.20168732797265232</v>
+      </c>
+      <c r="L11">
+        <v>0.20618189121783903</v>
+      </c>
+      <c r="N11">
+        <v>84</v>
+      </c>
+      <c r="O11">
+        <v>0.15048353300942274</v>
+      </c>
+      <c r="P11">
+        <v>0.15149439121783903</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B12">
         <v>7</v>
       </c>
@@ -853,14 +3771,29 @@
       <c r="D12">
         <v>7</v>
       </c>
+      <c r="F12">
+        <v>2.5298221281347035</v>
+      </c>
       <c r="J12">
         <v>86</v>
       </c>
       <c r="K12">
-        <v>0.26648097458621844</v>
+        <v>0.266480974586214</v>
+      </c>
+      <c r="L12">
+        <v>0.26086939121783903</v>
+      </c>
+      <c r="N12">
+        <v>85</v>
+      </c>
+      <c r="O12">
+        <v>0.20168732797265232</v>
+      </c>
+      <c r="P12">
+        <v>0.20618189121783903</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B13">
         <v>8</v>
       </c>
@@ -870,14 +3803,29 @@
       <c r="D13">
         <v>8</v>
       </c>
+      <c r="F13">
+        <v>3.1622776601683795</v>
+      </c>
       <c r="J13">
         <v>87</v>
       </c>
       <c r="K13">
-        <v>0.34730740212793787</v>
+        <v>0.34730740212793254</v>
+      </c>
+      <c r="L13">
+        <v>0.31555689121783903</v>
+      </c>
+      <c r="N13">
+        <v>86</v>
+      </c>
+      <c r="O13">
+        <v>0.266480974586214</v>
+      </c>
+      <c r="P13">
+        <v>0.26086939121783903</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B14">
         <v>9</v>
       </c>
@@ -893,8 +3841,20 @@
       <c r="K14">
         <v>0.44676133725329414</v>
       </c>
+      <c r="L14">
+        <v>0.40788732068490319</v>
+      </c>
+      <c r="N14">
+        <v>87</v>
+      </c>
+      <c r="O14">
+        <v>0.34730740212793254</v>
+      </c>
+      <c r="P14">
+        <v>0.31555689121783903</v>
+      </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B15">
         <v>10</v>
       </c>
@@ -910,257 +3870,653 @@
       <c r="K15">
         <v>0.56753930674006803</v>
       </c>
+      <c r="L15">
+        <v>0.57976232068490319</v>
+      </c>
+      <c r="N15">
+        <v>88</v>
+      </c>
+      <c r="O15">
+        <v>0.44676133725329414</v>
+      </c>
+      <c r="P15">
+        <v>0.40788732068490319</v>
+      </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J16">
         <v>90</v>
       </c>
       <c r="K16">
         <v>0.71238089607367172</v>
       </c>
+      <c r="L16">
+        <v>0.75163732068490319</v>
+      </c>
+      <c r="N16">
+        <v>89</v>
+      </c>
+      <c r="O16">
+        <v>0.56753930674006803</v>
+      </c>
+      <c r="P16">
+        <v>0.57976232068490319</v>
+      </c>
     </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J17">
         <v>91</v>
       </c>
       <c r="K17">
-        <v>0.88400364647703356</v>
+        <v>0.8840036464770229</v>
+      </c>
+      <c r="L17">
+        <v>0.92351232068490319</v>
+      </c>
+      <c r="N17">
+        <v>90</v>
+      </c>
+      <c r="O17">
+        <v>0.71238089607367172</v>
+      </c>
+      <c r="P17">
+        <v>0.75163732068490319</v>
       </c>
     </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J18">
         <v>92</v>
       </c>
       <c r="K18">
         <v>1.0850344779622993</v>
       </c>
+      <c r="L18">
+        <v>1.0953873206849032</v>
+      </c>
+      <c r="N18">
+        <v>91</v>
+      </c>
+      <c r="O18">
+        <v>0.8840036464770229</v>
+      </c>
+      <c r="P18">
+        <v>0.92351232068490319</v>
+      </c>
     </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J19">
         <v>93</v>
       </c>
       <c r="K19">
         <v>1.3179408286409817</v>
       </c>
+      <c r="L19">
+        <v>1.2672623206849032</v>
+      </c>
+      <c r="N19">
+        <v>92</v>
+      </c>
+      <c r="O19">
+        <v>1.0850344779622993</v>
+      </c>
+      <c r="P19">
+        <v>1.0953873206849032</v>
+      </c>
     </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J20">
         <v>94</v>
       </c>
       <c r="K20">
         <v>1.5849647756893894</v>
       </c>
+      <c r="L20">
+        <v>1.561530627262492</v>
+      </c>
+      <c r="N20">
+        <v>93</v>
+      </c>
+      <c r="O20">
+        <v>1.3179408286409817</v>
+      </c>
+      <c r="P20">
+        <v>1.2672623206849032</v>
+      </c>
     </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J21">
         <v>95</v>
       </c>
       <c r="K21">
         <v>1.8880632480607282</v>
       </c>
+      <c r="L21">
+        <v>1.938483752262492</v>
+      </c>
+      <c r="N21">
+        <v>94</v>
+      </c>
+      <c r="O21">
+        <v>1.5849647756893894</v>
+      </c>
+      <c r="P21">
+        <v>1.561530627262492</v>
+      </c>
     </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J22">
         <v>96</v>
       </c>
       <c r="K22">
         <v>2.2288570738163145</v>
       </c>
+      <c r="L22">
+        <v>2.315436877262492</v>
+      </c>
+      <c r="N22">
+        <v>95</v>
+      </c>
+      <c r="O22">
+        <v>1.8880632480607282</v>
+      </c>
+      <c r="P22">
+        <v>1.938483752262492</v>
+      </c>
     </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J23">
         <v>97</v>
       </c>
       <c r="K23">
         <v>2.6085910627585847</v>
       </c>
+      <c r="L23">
+        <v>2.692390002262492</v>
+      </c>
+      <c r="N23">
+        <v>96</v>
+      </c>
+      <c r="O23">
+        <v>2.2288570738163145</v>
+      </c>
+      <c r="P23">
+        <v>2.315436877262492</v>
+      </c>
     </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J24">
         <v>98</v>
       </c>
       <c r="K24">
         <v>3.0281066582734937</v>
       </c>
+      <c r="L24">
+        <v>3.069343127262492</v>
+      </c>
+      <c r="N24">
+        <v>97</v>
+      </c>
+      <c r="O24">
+        <v>2.6085910627585847</v>
+      </c>
+      <c r="P24">
+        <v>2.692390002262492</v>
+      </c>
     </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J25">
         <v>99</v>
       </c>
       <c r="K25">
         <v>3.4878279587501879</v>
       </c>
+      <c r="L25">
+        <v>3.446296252262492</v>
+      </c>
+      <c r="N25">
+        <v>98</v>
+      </c>
+      <c r="O25">
+        <v>3.0281066582734937</v>
+      </c>
+      <c r="P25">
+        <v>3.069343127262492</v>
+      </c>
     </row>
-    <row r="26" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
         <v>3.987761167674492</v>
       </c>
+      <c r="L26">
+        <v>3.9459687470320333</v>
+      </c>
+      <c r="N26">
+        <v>99</v>
+      </c>
+      <c r="O26">
+        <v>3.4878279587501879</v>
+      </c>
+      <c r="P26">
+        <v>3.446296252262492</v>
+      </c>
     </row>
-    <row r="27" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J27">
         <v>101</v>
       </c>
       <c r="K27">
         <v>4.5275068370385512</v>
       </c>
+      <c r="L27">
+        <v>4.5690156220320333</v>
+      </c>
+      <c r="N27">
+        <v>100</v>
+      </c>
+      <c r="O27">
+        <v>3.987761167674492</v>
+      </c>
+      <c r="P27">
+        <v>3.9459687470320333</v>
+      </c>
     </row>
-    <row r="28" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J28">
         <v>102</v>
       </c>
       <c r="K28">
         <v>5.1062836665495652</v>
       </c>
+      <c r="L28">
+        <v>5.1920624970320333</v>
+      </c>
+      <c r="N28">
+        <v>101</v>
+      </c>
+      <c r="O28">
+        <v>4.5275068370385512</v>
+      </c>
+      <c r="P28">
+        <v>4.5690156220320333</v>
+      </c>
     </row>
-    <row r="29" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J29">
         <v>103</v>
       </c>
       <c r="K29">
         <v>5.7229621445706016</v>
       </c>
+      <c r="L29">
+        <v>5.8151093720320333</v>
+      </c>
+      <c r="N29">
+        <v>102</v>
+      </c>
+      <c r="O29">
+        <v>5.1062836665495652</v>
+      </c>
+      <c r="P29">
+        <v>5.1920624970320333</v>
+      </c>
     </row>
-    <row r="30" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J30">
         <v>104</v>
       </c>
       <c r="K30">
         <v>6.376105985444056</v>
       </c>
+      <c r="L30">
+        <v>6.4381562470320333</v>
+      </c>
+      <c r="N30">
+        <v>103</v>
+      </c>
+      <c r="O30">
+        <v>5.7229621445706016</v>
+      </c>
+      <c r="P30">
+        <v>5.8151093720320333</v>
+      </c>
     </row>
-    <row r="31" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J31">
         <v>105</v>
       </c>
       <c r="K31">
         <v>7.0640191378988391</v>
       </c>
+      <c r="L31">
+        <v>7.0612031220320333</v>
+      </c>
+      <c r="N31">
+        <v>104</v>
+      </c>
+      <c r="O31">
+        <v>6.376105985444056</v>
+      </c>
+      <c r="P31">
+        <v>6.4381562470320333</v>
+      </c>
     </row>
-    <row r="32" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J32">
         <v>106</v>
       </c>
       <c r="K32">
         <v>7.7847961044341929</v>
       </c>
+      <c r="L32">
+        <v>7.6847395769465408</v>
+      </c>
+      <c r="N32">
+        <v>105</v>
+      </c>
+      <c r="O32">
+        <v>7.0640191378988391</v>
+      </c>
+      <c r="P32">
+        <v>7.0612031220320333</v>
+      </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J33">
         <v>107</v>
       </c>
       <c r="K33">
         <v>8.5363734057617648</v>
       </c>
+      <c r="L33">
+        <v>8.5128645769465408</v>
+      </c>
+      <c r="N33">
+        <v>106</v>
+      </c>
+      <c r="O33">
+        <v>7.7847961044341929</v>
+      </c>
+      <c r="P33">
+        <v>7.6847395769465408</v>
+      </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J34">
         <v>108</v>
       </c>
       <c r="K34">
         <v>9.3165802243033653</v>
       </c>
+      <c r="L34">
+        <v>9.3409895769465408</v>
+      </c>
+      <c r="N34">
+        <v>107</v>
+      </c>
+      <c r="O34">
+        <v>8.5363734057617648</v>
+      </c>
+      <c r="P34">
+        <v>8.5128645769465408</v>
+      </c>
     </row>
-    <row r="35" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J35">
         <v>109</v>
       </c>
       <c r="K35">
-        <v>10.123186539019287</v>
+        <v>10.123186539019301</v>
+      </c>
+      <c r="L35">
+        <v>10.169114576946541</v>
+      </c>
+      <c r="N35">
+        <v>108</v>
+      </c>
+      <c r="O35">
+        <v>9.3165802243033653</v>
+      </c>
+      <c r="P35">
+        <v>9.3409895769465408</v>
       </c>
     </row>
-    <row r="36" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J36">
         <v>110</v>
       </c>
       <c r="K36">
-        <v>10.953947391857227</v>
+        <v>10.953947391857241</v>
+      </c>
+      <c r="L36">
+        <v>10.997239576946541</v>
+      </c>
+      <c r="N36">
+        <v>109</v>
+      </c>
+      <c r="O36">
+        <v>10.123186539019301</v>
+      </c>
+      <c r="P36">
+        <v>10.169114576946541</v>
       </c>
     </row>
-    <row r="37" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J37">
         <v>111</v>
       </c>
       <c r="K37">
         <v>11.806642276452777</v>
       </c>
+      <c r="L37">
+        <v>11.825364576946541</v>
+      </c>
+      <c r="N37">
+        <v>110</v>
+      </c>
+      <c r="O37">
+        <v>10.953947391857241</v>
+      </c>
+      <c r="P37">
+        <v>10.997239576946541</v>
+      </c>
     </row>
-    <row r="38" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J38">
         <v>112</v>
       </c>
       <c r="K38">
         <v>12.679108988059141</v>
       </c>
+      <c r="L38">
+        <v>12.653489576946541</v>
+      </c>
+      <c r="N38">
+        <v>111</v>
+      </c>
+      <c r="O38">
+        <v>11.806642276452777</v>
+      </c>
+      <c r="P38">
+        <v>11.825364576946541</v>
+      </c>
     </row>
-    <row r="39" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J39">
         <v>113</v>
       </c>
       <c r="K39">
-        <v>13.569271600088328</v>
+        <v>13.569271600088314</v>
+      </c>
+      <c r="L39">
+        <v>13.49122085642486</v>
+      </c>
+      <c r="N39">
+        <v>112</v>
+      </c>
+      <c r="O39">
+        <v>12.679108988059141</v>
+      </c>
+      <c r="P39">
+        <v>12.653489576946541</v>
       </c>
     </row>
-    <row r="40" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J40">
         <v>114</v>
       </c>
       <c r="K40">
         <v>14.47516252219144</v>
       </c>
+      <c r="L40">
+        <v>14.43653335642486</v>
+      </c>
+      <c r="N40">
+        <v>113</v>
+      </c>
+      <c r="O40">
+        <v>13.569271600088314</v>
+      </c>
+      <c r="P40">
+        <v>13.49122085642486</v>
+      </c>
     </row>
-    <row r="41" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J41">
         <v>115</v>
       </c>
       <c r="K41">
         <v>15.394938837716396</v>
       </c>
+      <c r="L41">
+        <v>15.38184585642486</v>
+      </c>
+      <c r="N41">
+        <v>114</v>
+      </c>
+      <c r="O41">
+        <v>14.47516252219144</v>
+      </c>
+      <c r="P41">
+        <v>14.43653335642486</v>
+      </c>
     </row>
-    <row r="42" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J42">
         <v>116</v>
       </c>
       <c r="K42">
         <v>16.326893309710854</v>
       </c>
+      <c r="L42">
+        <v>16.32715835642486</v>
+      </c>
+      <c r="N42">
+        <v>115</v>
+      </c>
+      <c r="O42">
+        <v>15.394938837716396</v>
+      </c>
+      <c r="P42">
+        <v>15.38184585642486</v>
+      </c>
     </row>
-    <row r="43" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J43">
         <v>117</v>
       </c>
       <c r="K43">
         <v>17.269460583629098</v>
       </c>
+      <c r="L43">
+        <v>17.27247085642486</v>
+      </c>
+      <c r="N43">
+        <v>116</v>
+      </c>
+      <c r="O43">
+        <v>16.326893309710854</v>
+      </c>
+      <c r="P43">
+        <v>16.32715835642486</v>
+      </c>
     </row>
-    <row r="44" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J44">
         <v>118</v>
       </c>
       <c r="K44">
-        <v>18.221219204170339</v>
+        <v>18.221219204170353</v>
+      </c>
+      <c r="L44">
+        <v>18.21778335642486</v>
+      </c>
+      <c r="N44">
+        <v>117</v>
+      </c>
+      <c r="O44">
+        <v>17.269460583629098</v>
+      </c>
+      <c r="P44">
+        <v>17.27247085642486</v>
       </c>
     </row>
-    <row r="45" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J45">
         <v>119</v>
       </c>
       <c r="K45">
         <v>19.180890108309015</v>
       </c>
+      <c r="L45">
+        <v>19.16309585642486</v>
+      </c>
+      <c r="N45">
+        <v>118</v>
+      </c>
+      <c r="O45">
+        <v>18.221219204170353</v>
+      </c>
+      <c r="P45">
+        <v>18.21778335642486</v>
+      </c>
     </row>
-    <row r="46" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="10:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J46">
         <v>120</v>
       </c>
       <c r="K46">
         <v>20.14733226325697</v>
+      </c>
+      <c r="L46">
+        <v>20.10840835642486</v>
+      </c>
+      <c r="N46">
+        <v>119</v>
+      </c>
+      <c r="O46">
+        <v>19.180890108309015</v>
+      </c>
+      <c r="P46">
+        <v>19.16309585642486</v>
+      </c>
+    </row>
+    <row r="47" spans="10:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N47">
+        <v>120</v>
+      </c>
+      <c r="O47">
+        <v>20.14733226325697</v>
+      </c>
+      <c r="P47">
+        <v>20.10840835642486</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/xlsx/final.xlsx
+++ b/xlsx/final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17861\source\repos\6491-hw4\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577B1F70-273F-4940-A630-3577599AE07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA42428-BE0D-479C-B615-BD2D7947E8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5030" yWindow="1720" windowWidth="19200" windowHeight="11250" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
+    <workbookView xWindow="8910" yWindow="2955" windowWidth="28800" windowHeight="16335" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1689,10 +1689,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2011,14 +2007,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9333FE1-19FB-4A1D-86C4-C34A7A2ACCE3}">
   <dimension ref="B2:N46"/>
-  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.35546875" customWidth="1"/>
+    <col min="1" max="1" width="3.59765625" customWidth="1"/>
+    <col min="7" max="7" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2030,14 +2026,14 @@
       </c>
       <c r="F2" s="3" cm="1">
         <f t="array" ref="F2">_xll.\OPTION.DISCRETE(_xlfn.ANCHORARRAY(D5),_xlfn.ANCHORARRAY(C5))</f>
-        <v>2664391741632</v>
+        <v>1548661410784</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="3" cm="1">
         <f t="array" ref="H2">_xll.\OPTION.NORMAL()</f>
-        <v>2664307721504</v>
+        <v>1548017934512</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>5</v>
@@ -2046,7 +2042,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F3" cm="1">
         <f t="array" ref="F3:F13">_xll.OPTION.DISCRETE(discrete)</f>
         <v>-3.1622776601683795</v>
@@ -2062,7 +2058,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2083,13 +2079,13 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" cm="1">
         <f t="array" ref="B5:B15">_xlfn.SEQUENCE(n+1,1,0)</f>
         <v>0</v>
       </c>
       <c r="C5" cm="1">
-        <f t="array" ref="C5:C15">_xlfn.BINOM.DIST(_xlfn.ANCHORARRAY(B5),10,0.5,FALSE)</f>
+        <f t="array" ref="C5:C15">_xlfn.BINOM.DIST(_xlfn.ANCHORARRAY(B5),n,0.5,FALSE)</f>
         <v>9.765625E-4</v>
       </c>
       <c r="D5" cm="1">
@@ -2109,7 +2105,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1</v>
       </c>
@@ -2138,7 +2134,7 @@
         <v>3.4047379960682522E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2</v>
       </c>
@@ -2164,7 +2160,7 @@
         <v>4.4789567460682522E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>3</v>
       </c>
@@ -2190,7 +2186,7 @@
         <v>5.5531754960682522E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>4</v>
       </c>
@@ -2213,12 +2209,12 @@
         <v>9.6806891217839031E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10">
-        <v>0.24609375000000011</v>
+        <v>0.24609375000000008</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -2236,7 +2232,7 @@
         <v>0.15149439121783903</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>6</v>
       </c>
@@ -2259,7 +2255,7 @@
         <v>0.20618189121783903</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>7</v>
       </c>
@@ -2282,7 +2278,7 @@
         <v>0.26086939121783903</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>8</v>
       </c>
@@ -2305,7 +2301,7 @@
         <v>0.31555689121783903</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>9</v>
       </c>
@@ -2325,7 +2321,7 @@
         <v>0.40788732068490319</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>10</v>
       </c>
@@ -2345,7 +2341,7 @@
         <v>0.57976232068490319</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="J16">
         <v>90</v>
       </c>
@@ -2356,7 +2352,7 @@
         <v>0.75163732068490319</v>
       </c>
     </row>
-    <row r="17" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J17">
         <v>91</v>
       </c>
@@ -2367,7 +2363,7 @@
         <v>0.92351232068490319</v>
       </c>
     </row>
-    <row r="18" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J18">
         <v>92</v>
       </c>
@@ -2378,7 +2374,7 @@
         <v>1.0953873206849032</v>
       </c>
     </row>
-    <row r="19" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J19">
         <v>93</v>
       </c>
@@ -2389,7 +2385,7 @@
         <v>1.2672623206849032</v>
       </c>
     </row>
-    <row r="20" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J20">
         <v>94</v>
       </c>
@@ -2400,7 +2396,7 @@
         <v>1.561530627262492</v>
       </c>
     </row>
-    <row r="21" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J21">
         <v>95</v>
       </c>
@@ -2411,7 +2407,7 @@
         <v>1.938483752262492</v>
       </c>
     </row>
-    <row r="22" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J22">
         <v>96</v>
       </c>
@@ -2422,7 +2418,7 @@
         <v>2.315436877262492</v>
       </c>
     </row>
-    <row r="23" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J23">
         <v>97</v>
       </c>
@@ -2433,7 +2429,7 @@
         <v>2.692390002262492</v>
       </c>
     </row>
-    <row r="24" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J24">
         <v>98</v>
       </c>
@@ -2444,7 +2440,7 @@
         <v>3.069343127262492</v>
       </c>
     </row>
-    <row r="25" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J25">
         <v>99</v>
       </c>
@@ -2455,7 +2451,7 @@
         <v>3.446296252262492</v>
       </c>
     </row>
-    <row r="26" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J26">
         <v>100</v>
       </c>
@@ -2466,7 +2462,7 @@
         <v>3.9459687470320333</v>
       </c>
     </row>
-    <row r="27" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J27">
         <v>101</v>
       </c>
@@ -2477,7 +2473,7 @@
         <v>4.5690156220320333</v>
       </c>
     </row>
-    <row r="28" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J28">
         <v>102</v>
       </c>
@@ -2488,7 +2484,7 @@
         <v>5.1920624970320333</v>
       </c>
     </row>
-    <row r="29" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J29">
         <v>103</v>
       </c>
@@ -2499,7 +2495,7 @@
         <v>5.8151093720320333</v>
       </c>
     </row>
-    <row r="30" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J30">
         <v>104</v>
       </c>
@@ -2510,7 +2506,7 @@
         <v>6.4381562470320333</v>
       </c>
     </row>
-    <row r="31" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J31">
         <v>105</v>
       </c>
@@ -2521,7 +2517,7 @@
         <v>7.0612031220320333</v>
       </c>
     </row>
-    <row r="32" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J32">
         <v>106</v>
       </c>
@@ -2532,7 +2528,7 @@
         <v>7.6847395769465408</v>
       </c>
     </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="33" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J33">
         <v>107</v>
       </c>
@@ -2543,7 +2539,7 @@
         <v>8.5128645769465408</v>
       </c>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="34" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J34">
         <v>108</v>
       </c>
@@ -2554,7 +2550,7 @@
         <v>9.3409895769465408</v>
       </c>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="35" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J35">
         <v>109</v>
       </c>
@@ -2565,7 +2561,7 @@
         <v>10.169114576946541</v>
       </c>
     </row>
-    <row r="36" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="36" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J36">
         <v>110</v>
       </c>
@@ -2576,7 +2572,7 @@
         <v>10.997239576946541</v>
       </c>
     </row>
-    <row r="37" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J37">
         <v>111</v>
       </c>
@@ -2587,7 +2583,7 @@
         <v>11.825364576946541</v>
       </c>
     </row>
-    <row r="38" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="38" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J38">
         <v>112</v>
       </c>
@@ -2598,7 +2594,7 @@
         <v>12.653489576946541</v>
       </c>
     </row>
-    <row r="39" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="39" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J39">
         <v>113</v>
       </c>
@@ -2609,7 +2605,7 @@
         <v>13.49122085642486</v>
       </c>
     </row>
-    <row r="40" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="40" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J40">
         <v>114</v>
       </c>
@@ -2620,7 +2616,7 @@
         <v>14.43653335642486</v>
       </c>
     </row>
-    <row r="41" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J41">
         <v>115</v>
       </c>
@@ -2631,7 +2627,7 @@
         <v>15.38184585642486</v>
       </c>
     </row>
-    <row r="42" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="42" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J42">
         <v>116</v>
       </c>
@@ -2642,7 +2638,7 @@
         <v>16.32715835642486</v>
       </c>
     </row>
-    <row r="43" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="43" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J43">
         <v>117</v>
       </c>
@@ -2653,7 +2649,7 @@
         <v>17.27247085642486</v>
       </c>
     </row>
-    <row r="44" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="44" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J44">
         <v>118</v>
       </c>
@@ -2664,7 +2660,7 @@
         <v>18.21778335642486</v>
       </c>
     </row>
-    <row r="45" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="45" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J45">
         <v>119</v>
       </c>
@@ -2675,7 +2671,7 @@
         <v>19.16309585642486</v>
       </c>
     </row>
-    <row r="46" spans="10:12" x14ac:dyDescent="0.45">
+    <row r="46" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J46">
         <v>120</v>
       </c>

--- a/xlsx/final.xlsx
+++ b/xlsx/final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keith\source\repos\xlladdins\xll_ml\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gauravg\xll_ml\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFEF4C2-697C-475C-BFC8-0C347F24602F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77F3E93-5FB9-431B-914A-41C05EA148E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22875" windowHeight="13650" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -333,6 +330,1359 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.5247594050743651E-2"/>
+          <c:y val="0.17171296296296298"/>
+          <c:w val="0.88949759405074369"/>
+          <c:h val="0.6153546952464275"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$J$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>strike</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$J$6:$J$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-19DC-4999-9A45-9EAC515EBDE9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$K$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>normal_put</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$6:$K$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>3.9914343421845189E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7008934088098151E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0058534547871929E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11061799019468133</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15048353300942274</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20168732797265765</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26648097458621844</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34730740212793787</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.44676133725329414</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.56753930674006803</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71238089607367172</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.88400364647703356</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0850344779622993</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3179408286409817</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.5849647756893894</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.8880632480607282</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2288570738163145</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.6085910627585847</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0281066582734937</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.4878279587501879</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.987761167674492</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5275068370385512</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.1062836665495652</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.7229621445706016</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.376105985444056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0640191378988391</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.7847961044341929</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5363734057617648</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.3165802243033653</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.123186539019287</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.953947391857227</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.806642276452777</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.679108988059141</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.569271600088328</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.47516252219144</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.394938837716396</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.326893309710854</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.269460583629098</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.221219204170339</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.180890108309015</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20.14733226325697</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-19DC-4999-9A45-9EAC515EBDE9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$L$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>discrete_put</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$L$6:$L$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>3.4047379960682522E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4789567460682522E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5531754960682522E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6806891217839031E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15149439121783903</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20618189121783903</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26086939121783903</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.31555689121783903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40788732068490319</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.57976232068490319</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75163732068490319</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.92351232068490319</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0953873206849032</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2672623206849032</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.561530627262492</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.938483752262492</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.315436877262492</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.692390002262492</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.069343127262492</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.446296252262492</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.9459687470320333</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5690156220320333</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.1920624970320333</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.8151093720320333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.4381562470320333</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0612031220320333</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.6847395769465408</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5128645769465408</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.3409895769465408</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.169114576946541</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.997239576946541</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.825364576946541</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.653489576946541</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.49122085642486</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.43653335642486</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.38184585642486</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.32715835642486</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.27247085642486</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.21778335642486</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.16309585642486</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>20.10840835642486</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-19DC-4999-9A45-9EAC515EBDE9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1192695120"/>
+        <c:axId val="1192678800"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1192695120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1192678800"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1192678800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1192695120"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>292894</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>52388</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>588169</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>52388</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93617CA8-9D56-8B0F-3960-331CA74089F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -652,15 +2002,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9333FE1-19FB-4A1D-86C4-C34A7A2ACCE3}">
-  <dimension ref="B2:N46"/>
+  <dimension ref="B2:P46"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.578125" customWidth="1"/>
+    <col min="6" max="6" width="9.05078125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.68359375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.3671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -670,7 +2021,10 @@
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3" cm="1">
+        <f t="array" ref="F2:F13">_xll.\OPTION.DISCRETE(_xlfn.ANCHORARRAY(D5),_xlfn.ANCHORARRAY(C5))</f>
+        <v>2418610422832</v>
+      </c>
       <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
@@ -685,7 +2039,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="F3">
+        <v>-3.1622776601683795</v>
+      </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
@@ -693,13 +2050,16 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="F4">
+        <v>-2.5298221281347035</v>
+      </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
@@ -707,7 +2067,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" cm="1">
         <f t="array" ref="B5:B15">_xlfn.SEQUENCE(n+1,1,0)</f>
         <v>0</v>
@@ -720,6 +2080,9 @@
         <f t="array" ref="D5:D15">_xlfn.ANCHORARRAY(B5)</f>
         <v>0</v>
       </c>
+      <c r="F5">
+        <v>-1.8973665961010278</v>
+      </c>
       <c r="J5" s="1" t="s">
         <v>10</v>
       </c>
@@ -729,8 +2092,12 @@
       <c r="L5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="P5" cm="1">
+        <f t="array" ref="P5:P16">_xll.\OPTION.DISCRETE(D5:D15,C5:C15)</f>
+        <v>2419144591184</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B6">
         <v>1</v>
       </c>
@@ -739,6 +2106,9 @@
       </c>
       <c r="D6">
         <v>1</v>
+      </c>
+      <c r="F6">
+        <v>-1.2649110640673518</v>
       </c>
       <c r="I6">
         <v>80</v>
@@ -751,8 +2121,15 @@
         <f t="array" ref="K6:K46">_xlfn.MAP(_xlfn.ANCHORARRAY(J6),_xlfn.LAMBDA(_xlpm.k,_xll.OPTION.BLACK.PUT(f,s,_xlpm.k,normal)))</f>
         <v>3.9914343421845189E-2</v>
       </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L6" cm="1">
+        <f t="array" ref="L6:L46">_xlfn.MAP(_xlfn.ANCHORARRAY(J6),_xlfn.LAMBDA(_xlpm.k,_xll.OPTION.BLACK.PUT(f,s,_xlpm.k,discrete)))</f>
+        <v>3.4047379960682522E-2</v>
+      </c>
+      <c r="P6">
+        <v>-3.1622776601683795</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7">
         <v>2</v>
       </c>
@@ -762,6 +2139,9 @@
       <c r="D7">
         <v>2</v>
       </c>
+      <c r="F7">
+        <v>-0.63245553203367588</v>
+      </c>
       <c r="I7">
         <v>120</v>
       </c>
@@ -771,8 +2151,14 @@
       <c r="K7">
         <v>5.7008934088098151E-2</v>
       </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L7">
+        <v>4.4789567460682522E-2</v>
+      </c>
+      <c r="P7">
+        <v>-2.5298221281347035</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B8">
         <v>3</v>
       </c>
@@ -782,6 +2168,9 @@
       <c r="D8">
         <v>3</v>
       </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
       <c r="I8">
         <v>1</v>
       </c>
@@ -791,8 +2180,14 @@
       <c r="K8">
         <v>8.0058534547871929E-2</v>
       </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L8">
+        <v>5.5531754960682522E-2</v>
+      </c>
+      <c r="P8">
+        <v>-1.8973665961010278</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B9">
         <v>4</v>
       </c>
@@ -802,14 +2197,23 @@
       <c r="D9">
         <v>4</v>
       </c>
+      <c r="F9">
+        <v>0.63245553203367588</v>
+      </c>
       <c r="J9">
         <v>83</v>
       </c>
       <c r="K9">
         <v>0.11061799019468133</v>
       </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L9">
+        <v>9.6806891217839031E-2</v>
+      </c>
+      <c r="P9">
+        <v>-1.2649110640673518</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B10">
         <v>5</v>
       </c>
@@ -819,14 +2223,23 @@
       <c r="D10">
         <v>5</v>
       </c>
+      <c r="F10">
+        <v>1.2649110640673518</v>
+      </c>
       <c r="J10">
         <v>84</v>
       </c>
       <c r="K10">
         <v>0.15048353300942274</v>
       </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L10">
+        <v>0.15149439121783903</v>
+      </c>
+      <c r="P10">
+        <v>-0.63245553203367588</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B11">
         <v>6</v>
       </c>
@@ -836,14 +2249,23 @@
       <c r="D11">
         <v>6</v>
       </c>
+      <c r="F11">
+        <v>1.8973665961010278</v>
+      </c>
       <c r="J11">
         <v>85</v>
       </c>
       <c r="K11">
         <v>0.20168732797265765</v>
       </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L11">
+        <v>0.20618189121783903</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B12">
         <v>7</v>
       </c>
@@ -853,14 +2275,23 @@
       <c r="D12">
         <v>7</v>
       </c>
+      <c r="F12">
+        <v>2.5298221281347035</v>
+      </c>
       <c r="J12">
         <v>86</v>
       </c>
       <c r="K12">
         <v>0.26648097458621844</v>
       </c>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L12">
+        <v>0.26086939121783903</v>
+      </c>
+      <c r="P12">
+        <v>0.63245553203367588</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B13">
         <v>8</v>
       </c>
@@ -870,14 +2301,23 @@
       <c r="D13">
         <v>8</v>
       </c>
+      <c r="F13">
+        <v>3.1622776601683795</v>
+      </c>
       <c r="J13">
         <v>87</v>
       </c>
       <c r="K13">
         <v>0.34730740212793787</v>
       </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L13">
+        <v>0.31555689121783903</v>
+      </c>
+      <c r="P13">
+        <v>1.2649110640673518</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B14">
         <v>9</v>
       </c>
@@ -893,8 +2333,14 @@
       <c r="K14">
         <v>0.44676133725329414</v>
       </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L14">
+        <v>0.40788732068490319</v>
+      </c>
+      <c r="P14">
+        <v>1.8973665961010278</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B15">
         <v>10</v>
       </c>
@@ -910,257 +2356,360 @@
       <c r="K15">
         <v>0.56753930674006803</v>
       </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L15">
+        <v>0.57976232068490319</v>
+      </c>
+      <c r="P15">
+        <v>2.5298221281347035</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="J16">
         <v>90</v>
       </c>
       <c r="K16">
         <v>0.71238089607367172</v>
       </c>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L16">
+        <v>0.75163732068490319</v>
+      </c>
+      <c r="P16">
+        <v>3.1622776601683795</v>
+      </c>
+    </row>
+    <row r="17" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J17">
         <v>91</v>
       </c>
       <c r="K17">
         <v>0.88400364647703356</v>
       </c>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L17">
+        <v>0.92351232068490319</v>
+      </c>
+    </row>
+    <row r="18" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J18">
         <v>92</v>
       </c>
       <c r="K18">
         <v>1.0850344779622993</v>
       </c>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L18">
+        <v>1.0953873206849032</v>
+      </c>
+    </row>
+    <row r="19" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J19">
         <v>93</v>
       </c>
       <c r="K19">
         <v>1.3179408286409817</v>
       </c>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L19">
+        <v>1.2672623206849032</v>
+      </c>
+    </row>
+    <row r="20" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J20">
         <v>94</v>
       </c>
       <c r="K20">
         <v>1.5849647756893894</v>
       </c>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L20">
+        <v>1.561530627262492</v>
+      </c>
+    </row>
+    <row r="21" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J21">
         <v>95</v>
       </c>
       <c r="K21">
         <v>1.8880632480607282</v>
       </c>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L21">
+        <v>1.938483752262492</v>
+      </c>
+    </row>
+    <row r="22" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J22">
         <v>96</v>
       </c>
       <c r="K22">
         <v>2.2288570738163145</v>
       </c>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L22">
+        <v>2.315436877262492</v>
+      </c>
+    </row>
+    <row r="23" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J23">
         <v>97</v>
       </c>
       <c r="K23">
         <v>2.6085910627585847</v>
       </c>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L23">
+        <v>2.692390002262492</v>
+      </c>
+    </row>
+    <row r="24" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J24">
         <v>98</v>
       </c>
       <c r="K24">
         <v>3.0281066582734937</v>
       </c>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L24">
+        <v>3.069343127262492</v>
+      </c>
+    </row>
+    <row r="25" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J25">
         <v>99</v>
       </c>
       <c r="K25">
         <v>3.4878279587501879</v>
       </c>
-    </row>
-    <row r="26" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L25">
+        <v>3.446296252262492</v>
+      </c>
+    </row>
+    <row r="26" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
         <v>3.987761167674492</v>
       </c>
-    </row>
-    <row r="27" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L26">
+        <v>3.9459687470320333</v>
+      </c>
+    </row>
+    <row r="27" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J27">
         <v>101</v>
       </c>
       <c r="K27">
         <v>4.5275068370385512</v>
       </c>
-    </row>
-    <row r="28" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L27">
+        <v>4.5690156220320333</v>
+      </c>
+    </row>
+    <row r="28" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J28">
         <v>102</v>
       </c>
       <c r="K28">
         <v>5.1062836665495652</v>
       </c>
-    </row>
-    <row r="29" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L28">
+        <v>5.1920624970320333</v>
+      </c>
+    </row>
+    <row r="29" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J29">
         <v>103</v>
       </c>
       <c r="K29">
         <v>5.7229621445706016</v>
       </c>
-    </row>
-    <row r="30" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L29">
+        <v>5.8151093720320333</v>
+      </c>
+    </row>
+    <row r="30" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J30">
         <v>104</v>
       </c>
       <c r="K30">
         <v>6.376105985444056</v>
       </c>
-    </row>
-    <row r="31" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L30">
+        <v>6.4381562470320333</v>
+      </c>
+    </row>
+    <row r="31" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J31">
         <v>105</v>
       </c>
       <c r="K31">
         <v>7.0640191378988391</v>
       </c>
-    </row>
-    <row r="32" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L31">
+        <v>7.0612031220320333</v>
+      </c>
+    </row>
+    <row r="32" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J32">
         <v>106</v>
       </c>
       <c r="K32">
         <v>7.7847961044341929</v>
       </c>
-    </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L32">
+        <v>7.6847395769465408</v>
+      </c>
+    </row>
+    <row r="33" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J33">
         <v>107</v>
       </c>
       <c r="K33">
         <v>8.5363734057617648</v>
       </c>
-    </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L33">
+        <v>8.5128645769465408</v>
+      </c>
+    </row>
+    <row r="34" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J34">
         <v>108</v>
       </c>
       <c r="K34">
         <v>9.3165802243033653</v>
       </c>
-    </row>
-    <row r="35" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L34">
+        <v>9.3409895769465408</v>
+      </c>
+    </row>
+    <row r="35" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J35">
         <v>109</v>
       </c>
       <c r="K35">
         <v>10.123186539019287</v>
       </c>
-    </row>
-    <row r="36" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L35">
+        <v>10.169114576946541</v>
+      </c>
+    </row>
+    <row r="36" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J36">
         <v>110</v>
       </c>
       <c r="K36">
         <v>10.953947391857227</v>
       </c>
-    </row>
-    <row r="37" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L36">
+        <v>10.997239576946541</v>
+      </c>
+    </row>
+    <row r="37" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J37">
         <v>111</v>
       </c>
       <c r="K37">
         <v>11.806642276452777</v>
       </c>
-    </row>
-    <row r="38" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L37">
+        <v>11.825364576946541</v>
+      </c>
+    </row>
+    <row r="38" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J38">
         <v>112</v>
       </c>
       <c r="K38">
         <v>12.679108988059141</v>
       </c>
-    </row>
-    <row r="39" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L38">
+        <v>12.653489576946541</v>
+      </c>
+    </row>
+    <row r="39" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J39">
         <v>113</v>
       </c>
       <c r="K39">
         <v>13.569271600088328</v>
       </c>
-    </row>
-    <row r="40" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L39">
+        <v>13.49122085642486</v>
+      </c>
+    </row>
+    <row r="40" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J40">
         <v>114</v>
       </c>
       <c r="K40">
         <v>14.47516252219144</v>
       </c>
-    </row>
-    <row r="41" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L40">
+        <v>14.43653335642486</v>
+      </c>
+    </row>
+    <row r="41" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J41">
         <v>115</v>
       </c>
       <c r="K41">
         <v>15.394938837716396</v>
       </c>
-    </row>
-    <row r="42" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L41">
+        <v>15.38184585642486</v>
+      </c>
+    </row>
+    <row r="42" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J42">
         <v>116</v>
       </c>
       <c r="K42">
         <v>16.326893309710854</v>
       </c>
-    </row>
-    <row r="43" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L42">
+        <v>16.32715835642486</v>
+      </c>
+    </row>
+    <row r="43" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J43">
         <v>117</v>
       </c>
       <c r="K43">
         <v>17.269460583629098</v>
       </c>
-    </row>
-    <row r="44" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L43">
+        <v>17.27247085642486</v>
+      </c>
+    </row>
+    <row r="44" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J44">
         <v>118</v>
       </c>
       <c r="K44">
         <v>18.221219204170339</v>
       </c>
-    </row>
-    <row r="45" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L44">
+        <v>18.21778335642486</v>
+      </c>
+    </row>
+    <row r="45" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J45">
         <v>119</v>
       </c>
       <c r="K45">
         <v>19.180890108309015</v>
       </c>
-    </row>
-    <row r="46" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L45">
+        <v>19.16309585642486</v>
+      </c>
+    </row>
+    <row r="46" spans="10:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J46">
         <v>120</v>
       </c>
       <c r="K46">
         <v>20.14733226325697</v>
       </c>
+      <c r="L46">
+        <v>20.10840835642486</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/xlsx/final.xlsx
+++ b/xlsx/final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keith\source\repos\xlladdins\xll_ml\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFEF4C2-697C-475C-BFC8-0C347F24602F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3332798-89AC-41B9-BD2F-B2E68F701E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
   </bookViews>
@@ -21,6 +21,7 @@
     <definedName name="k">Sheet1!$J$4</definedName>
     <definedName name="n">Sheet1!$C$2</definedName>
     <definedName name="normal">Sheet1!$H$2</definedName>
+    <definedName name="q">Sheet1!$C$3</definedName>
     <definedName name="s">Sheet1!$J$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -95,21 +96,567 @@
         </r>
       </text>
     </comment>
-    <comment ref="L6" authorId="0" shapeId="0" xr:uid="{0C40FB78-1452-47ED-899C-1437529FCBA3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Put values using the discrete distribution.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N6" authorId="0" shapeId="0" xr:uid="{7D38816F-797C-4005-B396-65538BF6EEC5}">
+    <comment ref="M6" authorId="0" shapeId="0" xr:uid="{7D38816F-797C-4005-B396-65538BF6EEC5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{948F1A35-EA07-4F0C-A7EA-D9D80C66D1B8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{788B8FF4-BC7A-4E6F-BEE5-DB77ACF07B20}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{63C7AC69-5692-4A68-809F-273ACED1F0D4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{11AF8CCC-8ADC-472C-BB4A-534426A94226}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{11660E8A-ACA6-429A-823D-FEDBA30116C2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{482A11FE-B0C7-47E3-8095-2F21EF0A8A5B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="0" shapeId="0" xr:uid="{93B8B4EC-5BFF-47BD-8161-043A23A3D385}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{131F2563-41E8-4328-B06E-C93A5123D128}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M15" authorId="0" shapeId="0" xr:uid="{7E7E4EDF-039C-4088-ACF7-3811DFD8A48F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M16" authorId="0" shapeId="0" xr:uid="{8941F90E-A387-41F2-A843-269E153971E5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M17" authorId="0" shapeId="0" xr:uid="{DAB72AC2-8032-4871-8F4D-AFE9AFD0EB2E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{BD01DDE9-3DAB-44BF-89DD-98E253DEBB65}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M19" authorId="0" shapeId="0" xr:uid="{F9C0DD7B-DDCB-4C20-9ECE-489644134934}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M20" authorId="0" shapeId="0" xr:uid="{2911EA44-224C-492B-AA8D-C37896FBDDAD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M21" authorId="0" shapeId="0" xr:uid="{098B9975-1CE5-42CB-95CD-C7D086224DCA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M22" authorId="0" shapeId="0" xr:uid="{8BB8AA19-E00E-4DB5-89CE-6CA0BF1E7EAF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M23" authorId="0" shapeId="0" xr:uid="{83E5980A-DFC0-4C2C-BA2E-C2E1C5BD19FC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M24" authorId="0" shapeId="0" xr:uid="{99DAD293-43BB-483A-8355-1D87A0ACA6F7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M25" authorId="0" shapeId="0" xr:uid="{BA9413A2-6019-475B-ABFC-25C935166897}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M26" authorId="0" shapeId="0" xr:uid="{1C7453F4-1C77-4279-B5D3-21330CBCCE11}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M27" authorId="0" shapeId="0" xr:uid="{B282FDC3-5ECE-4BF7-9A71-23AA333110FA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M28" authorId="0" shapeId="0" xr:uid="{48C17137-4A05-4E08-BE1D-14C1E3D1BBB2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M29" authorId="0" shapeId="0" xr:uid="{3B0A10C4-0C28-4B10-803E-FEB426169088}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M30" authorId="0" shapeId="0" xr:uid="{8F2E62BE-1299-45E1-AFA5-52A5ED9906FD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{BD197020-E3B7-471B-BD0E-D8C90657C4A3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{E745CE40-15DD-4925-9AB2-22C3D16DA087}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M33" authorId="0" shapeId="0" xr:uid="{7103CD34-B603-4B47-8E3A-F1FBECB1B078}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M34" authorId="0" shapeId="0" xr:uid="{342FA18D-52A5-4583-B5DD-2F30569192E1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{D64C8F2C-3F8F-472C-8EC5-5BC298945F23}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M36" authorId="0" shapeId="0" xr:uid="{4B1AC3FE-3BEA-4EB0-831C-DAAC9B51AED7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M37" authorId="0" shapeId="0" xr:uid="{6BC8C3C7-C260-4BE8-86D7-6D5ED9C4877B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M38" authorId="0" shapeId="0" xr:uid="{CAE92B65-3279-4C38-9099-ED96714FE6B2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M39" authorId="0" shapeId="0" xr:uid="{CFF77CE5-7147-4B64-AF8A-0CA9E70975D3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M40" authorId="0" shapeId="0" xr:uid="{D6C16120-55FF-47A6-B859-0D0FA0214054}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M41" authorId="0" shapeId="0" xr:uid="{93D3C917-5DA8-40DB-B458-3EB58A37E989}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M42" authorId="0" shapeId="0" xr:uid="{BC269792-BE0A-4831-856A-F097DB0B7C00}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M43" authorId="0" shapeId="0" xr:uid="{7692FD37-D6BC-482D-8476-C0F47ECD127F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M44" authorId="0" shapeId="0" xr:uid="{F1166A42-025A-4C28-A876-F79EE4C4ECBD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M45" authorId="0" shapeId="0" xr:uid="{35CB3789-4B1A-44C2-9234-302DDEF74D67}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insert graph of strike versus normal and discrete put values.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M46" authorId="0" shapeId="0" xr:uid="{FDA964B7-2508-4461-9E45-863D41822A2C}">
       <text>
         <r>
           <rPr>
@@ -150,7 +697,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>n</t>
   </si>
@@ -183,6 +730,15 @@
   </si>
   <si>
     <t>strike</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>variance</t>
+  </si>
+  <si>
+    <t>q</t>
   </si>
 </sst>
 </file>
@@ -333,6 +889,1445 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$J$6:$J$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$M$6:$M$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.10000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.10000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.10000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.10000000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C8AB-4B8B-A769-411392FD0956}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$J$6:$J$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$N$6:$N$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>7.9194489539153368E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.5157059150708092E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.6105790893215045E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.5298976350343753E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.3517437577271633E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.9438096692167471E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.2141586538058234E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.2626459419069621E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.1758184629501041E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.0169263797967705E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.4628026813189908E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6728827067749532E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.7252026841150876E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9.6572218748917471E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.4894154709242715E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.7920844524101894E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.10000161751862045</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.10084778586724699</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.10061334017383813</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9.9377199121620463E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>9.9924494084906307E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.10218062182860853</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.103489164426445</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.1038878729008812</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.1033734265574499</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.10189875739562262</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.10329533688488482</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.10504821796277669</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.10610819639689921</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.10643754425537091</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.10596465442382622</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.1045664615820369</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.10548241109494871</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.10706139872342309</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.10812473634601119</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.10861339727042094</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.10843538591175529</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.10744257858758272</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.10681659237423599</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.10835965820573557</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.10953414985532098</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C8AB-4B8B-A769-411392FD0956}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1989014719"/>
+        <c:axId val="1989015679"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1989014719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="120"/>
+          <c:min val="80"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1989015679"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1989015679"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1989014719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>364331</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>90486</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>721518</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>90486</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE7A41F4-0CE0-08B9-5AC5-87923C9D9290}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -656,6 +2651,7 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.578125" customWidth="1"/>
+    <col min="6" max="6" width="9.05078125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.68359375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.3671875" customWidth="1"/>
   </cols>
@@ -665,18 +2661,21 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3" cm="1">
+        <f t="array" ref="F2">_xll.\OPTION.DISCRETE(_xlfn.ANCHORARRAY(D5),_xlfn.ANCHORARRAY(C5))</f>
+        <v>2042332648176</v>
+      </c>
       <c r="G2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="3" cm="1">
         <f t="array" ref="H2">_xll.\OPTION.NORMAL()</f>
-        <v>1490952485744</v>
+        <v>2044155535952</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>5</v>
@@ -686,6 +2685,12 @@
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>0.2</v>
+      </c>
       <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
@@ -700,6 +2705,12 @@
       <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
@@ -709,16 +2720,28 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" cm="1">
-        <f t="array" ref="B5:B15">_xlfn.SEQUENCE(n+1,1,0)</f>
+        <f t="array" ref="B5:B25">_xlfn.SEQUENCE(n+1,1,0)</f>
         <v>0</v>
       </c>
       <c r="C5" cm="1">
-        <f t="array" ref="C5:C15">_xlfn.BINOM.DIST(_xlfn.ANCHORARRAY(B5),10,0.5,FALSE)</f>
-        <v>9.765625E-4</v>
+        <f t="array" ref="C5:C25">_xlfn.MAP(_xlfn.ANCHORARRAY(B5),_xlfn.LAMBDA(_xlpm.m,_xlfn.BINOM.DIST(_xlpm.m,n,q,FALSE)))</f>
+        <v>1.1529215046068471E-2</v>
       </c>
       <c r="D5" cm="1">
-        <f t="array" ref="D5:D15">_xlfn.ANCHORARRAY(B5)</f>
+        <f t="array" ref="D5:D25">_xlfn.ANCHORARRAY(B5)</f>
         <v>0</v>
+      </c>
+      <c r="F5" cm="1">
+        <f t="array" ref="F5:F25">_xll.OPTION.DISCRETE(discrete)</f>
+        <v>-2.2360679774997889</v>
+      </c>
+      <c r="G5">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(F5),_xlfn.ANCHORARRAY(C5))</f>
+        <v>1.0733619282401028E-15</v>
+      </c>
+      <c r="H5">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(F5),_xlfn.ANCHORARRAY(F5),_xlfn.ANCHORARRAY(C5))</f>
+        <v>1.0000000000000002</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>10</v>
@@ -735,10 +2758,13 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>9.7656250000000017E-3</v>
+        <v>5.7646075230342327E-2</v>
       </c>
       <c r="D6">
         <v>1</v>
+      </c>
+      <c r="F6">
+        <v>-1.6770509831248415</v>
       </c>
       <c r="I6">
         <v>80</v>
@@ -748,8 +2774,20 @@
         <v>80</v>
       </c>
       <c r="K6" cm="1">
-        <f t="array" ref="K6:K46">_xlfn.MAP(_xlfn.ANCHORARRAY(J6),_xlfn.LAMBDA(_xlpm.k,_xll.OPTION.BLACK.PUT(f,s,_xlpm.k,normal)))</f>
+        <f t="array" ref="K6:K46">_xlfn.MAP(_xlfn.ANCHORARRAY($J6),_xlfn.LAMBDA(_xlpm.k,_xll.OPTION.BLACK.PUT(f,s,_xlpm.k,normal)))</f>
         <v>3.9914343421845189E-2</v>
+      </c>
+      <c r="L6" cm="1">
+        <f t="array" ref="L6:L46">_xlfn.MAP(_xlfn.ANCHORARRAY($J6),_xlfn.LAMBDA(_xlpm.k,_xll.OPTION.BLACK.PUT(f,s,_xlpm.k,discrete)))</f>
+        <v>5.0765341236550521E-3</v>
+      </c>
+      <c r="M6" cm="1">
+        <f t="array" ref="M6">_xll.OPTION.BLACK.PUT_IMPLIED(f, K6, J6)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N6" cm="1">
+        <f t="array" ref="N6">_xll.OPTION.BLACK.PUT_IMPLIED(f, L6,J6)</f>
+        <v>7.9194489539153368E-2</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -757,11 +2795,14 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>4.3945312499999972E-2</v>
+        <v>0.1369094286720631</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
+      <c r="F7">
+        <v>-1.118033988749894</v>
+      </c>
       <c r="I7">
         <v>120</v>
       </c>
@@ -770,6 +2811,17 @@
       </c>
       <c r="K7">
         <v>5.7008934088098151E-2</v>
+      </c>
+      <c r="L7">
+        <v>1.660574916972346E-2</v>
+      </c>
+      <c r="M7" cm="1">
+        <f t="array" ref="M7">_xll.OPTION.BLACK.PUT_IMPLIED(f, K7, J7)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N7" cm="1">
+        <f t="array" ref="N7">_xll.OPTION.BLACK.PUT_IMPLIED(f, L7,J7)</f>
+        <v>8.5157059150708092E-2</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -777,11 +2829,14 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>0.11718750000000003</v>
+        <v>0.20536414300809455</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
+      <c r="F8">
+        <v>-0.55901699437494656</v>
+      </c>
       <c r="I8">
         <v>1</v>
       </c>
@@ -790,6 +2845,17 @@
       </c>
       <c r="K8">
         <v>8.0058534547871929E-2</v>
+      </c>
+      <c r="L8">
+        <v>2.813496421579198E-2</v>
+      </c>
+      <c r="M8" cm="1">
+        <f t="array" ref="M8">_xll.OPTION.BLACK.PUT_IMPLIED(f, K8, J8)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N8" cm="1">
+        <f t="array" ref="N8">_xll.OPTION.BLACK.PUT_IMPLIED(f, L8,J8)</f>
+        <v>8.6105790893215045E-2</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -797,16 +2863,30 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>0.20507812500000006</v>
+        <v>0.21819940194610055</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
+      <c r="F9">
+        <v>9.9301366129890944E-16</v>
+      </c>
       <c r="J9">
         <v>83</v>
       </c>
       <c r="K9">
         <v>0.11061799019468133</v>
+      </c>
+      <c r="L9">
+        <v>3.9664179261860388E-2</v>
+      </c>
+      <c r="M9" cm="1">
+        <f t="array" ref="M9">_xll.OPTION.BLACK.PUT_IMPLIED(f, K9, J9)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N9" cm="1">
+        <f t="array" ref="N9">_xll.OPTION.BLACK.PUT_IMPLIED(f, L9,J9)</f>
+        <v>8.5298976350343753E-2</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -814,16 +2894,30 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>0.24609375000000011</v>
+        <v>0.17455952155688043</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
+      <c r="F10">
+        <v>0.55901699437494845</v>
+      </c>
       <c r="J10">
         <v>84</v>
       </c>
       <c r="K10">
         <v>0.15048353300942274</v>
+      </c>
+      <c r="L10">
+        <v>5.1193394307928908E-2</v>
+      </c>
+      <c r="M10" cm="1">
+        <f t="array" ref="M10">_xll.OPTION.BLACK.PUT_IMPLIED(f, K10, J10)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N10" cm="1">
+        <f t="array" ref="N10">_xll.OPTION.BLACK.PUT_IMPLIED(f, L10,J10)</f>
+        <v>8.3517437577271633E-2</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -831,16 +2925,30 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>0.20507812500000006</v>
+        <v>0.1090997009730503</v>
       </c>
       <c r="D11">
         <v>6</v>
       </c>
+      <c r="F11">
+        <v>1.118033988749896</v>
+      </c>
       <c r="J11">
         <v>85</v>
       </c>
       <c r="K11">
         <v>0.20168732797265765</v>
+      </c>
+      <c r="L11">
+        <v>0.11265198626217554</v>
+      </c>
+      <c r="M11" cm="1">
+        <f t="array" ref="M11">_xll.OPTION.BLACK.PUT_IMPLIED(f, K11, J11)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N11" cm="1">
+        <f t="array" ref="N11">_xll.OPTION.BLACK.PUT_IMPLIED(f, L11,J11)</f>
+        <v>8.9438096692167471E-2</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -848,16 +2956,30 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>0.11718750000000003</v>
+        <v>5.4549850486525116E-2</v>
       </c>
       <c r="D12">
         <v>7</v>
       </c>
+      <c r="F12">
+        <v>1.6770509831248435</v>
+      </c>
       <c r="J12">
         <v>86</v>
       </c>
       <c r="K12">
         <v>0.26648097458621844</v>
+      </c>
+      <c r="L12">
+        <v>0.18182727653858599</v>
+      </c>
+      <c r="M12" cm="1">
+        <f t="array" ref="M12">_xll.OPTION.BLACK.PUT_IMPLIED(f, K12, J12)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N12" cm="1">
+        <f t="array" ref="N12">_xll.OPTION.BLACK.PUT_IMPLIED(f, L12,J12)</f>
+        <v>9.2141586538058234E-2</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -865,16 +2987,30 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>4.3945312499999986E-2</v>
+        <v>2.2160876760150834E-2</v>
       </c>
       <c r="D13">
         <v>8</v>
       </c>
+      <c r="F13">
+        <v>2.2360679774997911</v>
+      </c>
       <c r="J13">
         <v>87</v>
       </c>
       <c r="K13">
         <v>0.34730740212793787</v>
+      </c>
+      <c r="L13">
+        <v>0.25100256681499644</v>
+      </c>
+      <c r="M13" cm="1">
+        <f t="array" ref="M13">_xll.OPTION.BLACK.PUT_IMPLIED(f, K13, J13)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N13" cm="1">
+        <f t="array" ref="N13">_xll.OPTION.BLACK.PUT_IMPLIED(f, L13,J13)</f>
+        <v>9.2626459419069621E-2</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -882,16 +3018,30 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>9.7656250000000017E-3</v>
+        <v>7.386958920050278E-3</v>
       </c>
       <c r="D14">
         <v>9</v>
       </c>
+      <c r="F14">
+        <v>2.7950849718747386</v>
+      </c>
       <c r="J14">
         <v>88</v>
       </c>
       <c r="K14">
         <v>0.44676133725329414</v>
+      </c>
+      <c r="L14">
+        <v>0.32017785709140778</v>
+      </c>
+      <c r="M14" cm="1">
+        <f t="array" ref="M14">_xll.OPTION.BLACK.PUT_IMPLIED(f, K14, J14)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N14" cm="1">
+        <f t="array" ref="N14">_xll.OPTION.BLACK.PUT_IMPLIED(f, L14,J14)</f>
+        <v>9.1758184629501041E-2</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -899,268 +3049,744 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>9.765625E-4</v>
+        <v>2.0314137030138257E-3</v>
       </c>
       <c r="D15">
         <v>10</v>
       </c>
+      <c r="F15">
+        <v>3.354101966249686</v>
+      </c>
       <c r="J15">
         <v>89</v>
       </c>
       <c r="K15">
         <v>0.56753930674006803</v>
       </c>
+      <c r="L15">
+        <v>0.39331904396025408</v>
+      </c>
+      <c r="M15" cm="1">
+        <f t="array" ref="M15">_xll.OPTION.BLACK.PUT_IMPLIED(f, K15, J15)</f>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="N15" cm="1">
+        <f t="array" ref="N15">_xll.OPTION.BLACK.PUT_IMPLIED(f, L15,J15)</f>
+        <v>9.0169263797967705E-2</v>
+      </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16">
+        <v>11</v>
+      </c>
+      <c r="C16">
+        <v>4.6168493250314227E-4</v>
+      </c>
+      <c r="D16">
+        <v>11</v>
+      </c>
+      <c r="F16">
+        <v>3.9131189606246335</v>
+      </c>
       <c r="J16">
         <v>90</v>
       </c>
       <c r="K16">
         <v>0.71238089607367172</v>
       </c>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L16">
+        <v>0.59940376290872877</v>
+      </c>
+      <c r="M16" cm="1">
+        <f t="array" ref="M16">_xll.OPTION.BLACK.PUT_IMPLIED(f, K16, J16)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N16" cm="1">
+        <f t="array" ref="N16">_xll.OPTION.BLACK.PUT_IMPLIED(f, L16,J16)</f>
+        <v>9.4628026813189908E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>8.6565924844339142E-5</v>
+      </c>
+      <c r="D17">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>4.4721359549995814</v>
+      </c>
       <c r="J17">
         <v>91</v>
       </c>
       <c r="K17">
         <v>0.88400364647703356</v>
       </c>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L17">
+        <v>0.80548848185720345</v>
+      </c>
+      <c r="M17" cm="1">
+        <f t="array" ref="M17">_xll.OPTION.BLACK.PUT_IMPLIED(f, K17, J17)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N17" cm="1">
+        <f t="array" ref="N17">_xll.OPTION.BLACK.PUT_IMPLIED(f, L17,J17)</f>
+        <v>9.6728827067749532E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>1.3317834591436786E-5</v>
+      </c>
+      <c r="D18">
+        <v>13</v>
+      </c>
+      <c r="F18">
+        <v>5.0311529493745288</v>
+      </c>
       <c r="J18">
         <v>92</v>
       </c>
       <c r="K18">
         <v>1.0850344779622993</v>
       </c>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L18">
+        <v>1.0115732008056781</v>
+      </c>
+      <c r="M18" cm="1">
+        <f t="array" ref="M18">_xll.OPTION.BLACK.PUT_IMPLIED(f, K18, J18)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N18" cm="1">
+        <f t="array" ref="N18">_xll.OPTION.BLACK.PUT_IMPLIED(f, L18,J18)</f>
+        <v>9.7252026841150876E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19">
+        <v>1.6647293239295963E-6</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
+      <c r="F19">
+        <v>5.5901699437494763</v>
+      </c>
       <c r="J19">
         <v>93</v>
       </c>
       <c r="K19">
         <v>1.3179408286409817</v>
       </c>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L19">
+        <v>1.2176579197541493</v>
+      </c>
+      <c r="M19" cm="1">
+        <f t="array" ref="M19">_xll.OPTION.BLACK.PUT_IMPLIED(f, K19, J19)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N19" cm="1">
+        <f t="array" ref="N19">_xll.OPTION.BLACK.PUT_IMPLIED(f, L19,J19)</f>
+        <v>9.6572218748917471E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20">
+        <v>1.6647293239296003E-7</v>
+      </c>
+      <c r="D20">
+        <v>15</v>
+      </c>
+      <c r="F20">
+        <v>6.1491869381244237</v>
+      </c>
       <c r="J20">
         <v>94</v>
       </c>
       <c r="K20">
         <v>1.5849647756893894</v>
       </c>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L20">
+        <v>1.423742638702624</v>
+      </c>
+      <c r="M20" cm="1">
+        <f t="array" ref="M20">_xll.OPTION.BLACK.PUT_IMPLIED(f, K20, J20)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N20" cm="1">
+        <f t="array" ref="N20">_xll.OPTION.BLACK.PUT_IMPLIED(f, L20,J20)</f>
+        <v>9.4894154709242715E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <v>1.3005697843199991E-8</v>
+      </c>
+      <c r="D21">
+        <v>16</v>
+      </c>
+      <c r="F21">
+        <v>6.7082039324993712</v>
+      </c>
       <c r="J21">
         <v>95</v>
       </c>
       <c r="K21">
         <v>1.8880632480607282</v>
       </c>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L21">
+        <v>1.8174667451742721</v>
+      </c>
+      <c r="M21" cm="1">
+        <f t="array" ref="M21">_xll.OPTION.BLACK.PUT_IMPLIED(f, K21, J21)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N21" cm="1">
+        <f t="array" ref="N21">_xll.OPTION.BLACK.PUT_IMPLIED(f, L21,J21)</f>
+        <v>9.7920844524101894E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22">
+        <v>17</v>
+      </c>
+      <c r="C22">
+        <v>7.6504104960000131E-10</v>
+      </c>
+      <c r="D22">
+        <v>17</v>
+      </c>
+      <c r="F22">
+        <v>7.2672209268743186</v>
+      </c>
       <c r="J22">
         <v>96</v>
       </c>
       <c r="K22">
         <v>2.2288570738163145</v>
       </c>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L22">
+        <v>2.228915607130844</v>
+      </c>
+      <c r="M22" cm="1">
+        <f t="array" ref="M22">_xll.OPTION.BLACK.PUT_IMPLIED(f, K22, J22)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N22" cm="1">
+        <f t="array" ref="N22">_xll.OPTION.BLACK.PUT_IMPLIED(f, L22,J22)</f>
+        <v>0.10000161751862045</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23">
+        <v>18</v>
+      </c>
+      <c r="C23">
+        <v>3.1876710399999934E-11</v>
+      </c>
+      <c r="D23">
+        <v>18</v>
+      </c>
+      <c r="F23">
+        <v>7.8262379212492661</v>
+      </c>
       <c r="J23">
         <v>97</v>
       </c>
       <c r="K23">
         <v>2.6085910627585847</v>
       </c>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L23">
+        <v>2.6403644690874088</v>
+      </c>
+      <c r="M23" cm="1">
+        <f t="array" ref="M23">_xll.OPTION.BLACK.PUT_IMPLIED(f, K23, J23)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N23" cm="1">
+        <f t="array" ref="N23">_xll.OPTION.BLACK.PUT_IMPLIED(f, L23,J23)</f>
+        <v>0.10084778586724699</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24">
+        <v>19</v>
+      </c>
+      <c r="C24">
+        <v>8.3886079999999947E-13</v>
+      </c>
+      <c r="D24">
+        <v>19</v>
+      </c>
+      <c r="F24">
+        <v>8.3852549156242144</v>
+      </c>
       <c r="J24">
         <v>98</v>
       </c>
       <c r="K24">
         <v>3.0281066582734937</v>
       </c>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L24">
+        <v>3.0518133310439808</v>
+      </c>
+      <c r="M24" cm="1">
+        <f t="array" ref="M24">_xll.OPTION.BLACK.PUT_IMPLIED(f, K24, J24)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N24" cm="1">
+        <f t="array" ref="N24">_xll.OPTION.BLACK.PUT_IMPLIED(f, L24,J24)</f>
+        <v>0.10061334017383813</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25">
+        <v>20</v>
+      </c>
+      <c r="C25">
+        <v>1.048576000000001E-14</v>
+      </c>
+      <c r="D25">
+        <v>20</v>
+      </c>
+      <c r="F25">
+        <v>8.944271909999161</v>
+      </c>
       <c r="J25">
         <v>99</v>
       </c>
       <c r="K25">
         <v>3.4878279587501879</v>
       </c>
-    </row>
-    <row r="26" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L25">
+        <v>3.4632621930005456</v>
+      </c>
+      <c r="M25" cm="1">
+        <f t="array" ref="M25">_xll.OPTION.BLACK.PUT_IMPLIED(f, K25, J25)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N25" cm="1">
+        <f t="array" ref="N25">_xll.OPTION.BLACK.PUT_IMPLIED(f, L25,J25)</f>
+        <v>9.9377199121620463E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
         <v>3.987761167674492</v>
       </c>
-    </row>
-    <row r="27" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L26">
+        <v>3.9847530690023021</v>
+      </c>
+      <c r="M26" cm="1">
+        <f t="array" ref="M26">_xll.OPTION.BLACK.PUT_IMPLIED(f, K26, J26)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N26" cm="1">
+        <f t="array" ref="N26">_xll.OPTION.BLACK.PUT_IMPLIED(f, L26,J26)</f>
+        <v>9.9924494084906307E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J27">
         <v>101</v>
       </c>
       <c r="K27">
         <v>4.5275068370385512</v>
       </c>
-    </row>
-    <row r="28" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L27">
+        <v>4.6144013329049685</v>
+      </c>
+      <c r="M27" cm="1">
+        <f t="array" ref="M27">_xll.OPTION.BLACK.PUT_IMPLIED(f, K27, J27)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N27" cm="1">
+        <f t="array" ref="N27">_xll.OPTION.BLACK.PUT_IMPLIED(f, L27,J27)</f>
+        <v>0.10218062182860853</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J28">
         <v>102</v>
       </c>
       <c r="K28">
         <v>5.1062836665495652</v>
       </c>
-    </row>
-    <row r="29" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L28">
+        <v>5.2440495968076348</v>
+      </c>
+      <c r="M28" cm="1">
+        <f t="array" ref="M28">_xll.OPTION.BLACK.PUT_IMPLIED(f, K28, J28)</f>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="N28" cm="1">
+        <f t="array" ref="N28">_xll.OPTION.BLACK.PUT_IMPLIED(f, L28,J28)</f>
+        <v>0.103489164426445</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J29">
         <v>103</v>
       </c>
       <c r="K29">
         <v>5.7229621445706016</v>
       </c>
-    </row>
-    <row r="30" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L29">
+        <v>5.8736978607103012</v>
+      </c>
+      <c r="M29" cm="1">
+        <f t="array" ref="M29">_xll.OPTION.BLACK.PUT_IMPLIED(f, K29, J29)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N29" cm="1">
+        <f t="array" ref="N29">_xll.OPTION.BLACK.PUT_IMPLIED(f, L29,J29)</f>
+        <v>0.1038878729008812</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J30">
         <v>104</v>
       </c>
       <c r="K30">
         <v>6.376105985444056</v>
       </c>
-    </row>
-    <row r="31" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L30">
+        <v>6.5033461246129818</v>
+      </c>
+      <c r="M30" cm="1">
+        <f t="array" ref="M30">_xll.OPTION.BLACK.PUT_IMPLIED(f, K30, J30)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N30" cm="1">
+        <f t="array" ref="N30">_xll.OPTION.BLACK.PUT_IMPLIED(f, L30,J30)</f>
+        <v>0.1033734265574499</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J31">
         <v>105</v>
       </c>
       <c r="K31">
         <v>7.0640191378988391</v>
       </c>
-    </row>
-    <row r="32" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L31">
+        <v>7.1329943885156482</v>
+      </c>
+      <c r="M31" cm="1">
+        <f t="array" ref="M31">_xll.OPTION.BLACK.PUT_IMPLIED(f, K31, J31)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N31" cm="1">
+        <f t="array" ref="N31">_xll.OPTION.BLACK.PUT_IMPLIED(f, L31,J31)</f>
+        <v>0.10189875739562262</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J32">
         <v>106</v>
       </c>
       <c r="K32">
         <v>7.7847961044341929</v>
       </c>
-    </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L32">
+        <v>7.8994870360806999</v>
+      </c>
+      <c r="M32" cm="1">
+        <f t="array" ref="M32">_xll.OPTION.BLACK.PUT_IMPLIED(f, K32, J32)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N32" cm="1">
+        <f t="array" ref="N32">_xll.OPTION.BLACK.PUT_IMPLIED(f, L32,J32)</f>
+        <v>0.10329533688488482</v>
+      </c>
+    </row>
+    <row r="33" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J33">
         <v>107</v>
       </c>
       <c r="K33">
         <v>8.5363734057617648</v>
       </c>
-    </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L33">
+        <v>8.7036948215402532</v>
+      </c>
+      <c r="M33" cm="1">
+        <f t="array" ref="M33">_xll.OPTION.BLACK.PUT_IMPLIED(f, K33, J33)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N33" cm="1">
+        <f t="array" ref="N33">_xll.OPTION.BLACK.PUT_IMPLIED(f, L33,J33)</f>
+        <v>0.10504821796277669</v>
+      </c>
+    </row>
+    <row r="34" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J34">
         <v>108</v>
       </c>
       <c r="K34">
         <v>9.3165802243033653</v>
       </c>
-    </row>
-    <row r="35" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L34">
+        <v>9.5079026069997923</v>
+      </c>
+      <c r="M34" cm="1">
+        <f t="array" ref="M34">_xll.OPTION.BLACK.PUT_IMPLIED(f, K34, J34)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N34" cm="1">
+        <f t="array" ref="N34">_xll.OPTION.BLACK.PUT_IMPLIED(f, L34,J34)</f>
+        <v>0.10610819639689921</v>
+      </c>
+    </row>
+    <row r="35" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J35">
         <v>109</v>
       </c>
       <c r="K35">
         <v>10.123186539019287</v>
       </c>
-    </row>
-    <row r="36" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L35">
+        <v>10.312110392459346</v>
+      </c>
+      <c r="M35" cm="1">
+        <f t="array" ref="M35">_xll.OPTION.BLACK.PUT_IMPLIED(f, K35, J35)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N35" cm="1">
+        <f t="array" ref="N35">_xll.OPTION.BLACK.PUT_IMPLIED(f, L35,J35)</f>
+        <v>0.10643754425537091</v>
+      </c>
+    </row>
+    <row r="36" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J36">
         <v>110</v>
       </c>
       <c r="K36">
         <v>10.953947391857227</v>
       </c>
-    </row>
-    <row r="37" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L36">
+        <v>11.116318177918899</v>
+      </c>
+      <c r="M36" cm="1">
+        <f t="array" ref="M36">_xll.OPTION.BLACK.PUT_IMPLIED(f, K36, J36)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N36" cm="1">
+        <f t="array" ref="N36">_xll.OPTION.BLACK.PUT_IMPLIED(f, L36,J36)</f>
+        <v>0.10596465442382622</v>
+      </c>
+    </row>
+    <row r="37" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J37">
         <v>111</v>
       </c>
       <c r="K37">
         <v>11.806642276452777</v>
       </c>
-    </row>
-    <row r="38" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L37">
+        <v>11.920525963378452</v>
+      </c>
+      <c r="M37" cm="1">
+        <f t="array" ref="M37">_xll.OPTION.BLACK.PUT_IMPLIED(f, K37, J37)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N37" cm="1">
+        <f t="array" ref="N37">_xll.OPTION.BLACK.PUT_IMPLIED(f, L37,J37)</f>
+        <v>0.1045664615820369</v>
+      </c>
+    </row>
+    <row r="38" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J38">
         <v>112</v>
       </c>
       <c r="K38">
         <v>12.679108988059141</v>
       </c>
-    </row>
-    <row r="39" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L38">
+        <v>12.804886876992654</v>
+      </c>
+      <c r="M38" cm="1">
+        <f t="array" ref="M38">_xll.OPTION.BLACK.PUT_IMPLIED(f, K38, J38)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N38" cm="1">
+        <f t="array" ref="N38">_xll.OPTION.BLACK.PUT_IMPLIED(f, L38,J38)</f>
+        <v>0.10548241109494871</v>
+      </c>
+    </row>
+    <row r="39" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J39">
         <v>113</v>
       </c>
       <c r="K39">
         <v>13.569271600088328</v>
       </c>
-    </row>
-    <row r="40" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L39">
+        <v>13.718194363425255</v>
+      </c>
+      <c r="M39" cm="1">
+        <f t="array" ref="M39">_xll.OPTION.BLACK.PUT_IMPLIED(f, K39, J39)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N39" cm="1">
+        <f t="array" ref="N39">_xll.OPTION.BLACK.PUT_IMPLIED(f, L39,J39)</f>
+        <v>0.10706139872342309</v>
+      </c>
+    </row>
+    <row r="40" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J40">
         <v>114</v>
       </c>
       <c r="K40">
         <v>14.47516252219144</v>
       </c>
-    </row>
-    <row r="41" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L40">
+        <v>14.631501849857855</v>
+      </c>
+      <c r="M40" cm="1">
+        <f t="array" ref="M40">_xll.OPTION.BLACK.PUT_IMPLIED(f, K40, J40)</f>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="N40" cm="1">
+        <f t="array" ref="N40">_xll.OPTION.BLACK.PUT_IMPLIED(f, L40,J40)</f>
+        <v>0.10812473634601119</v>
+      </c>
+    </row>
+    <row r="41" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J41">
         <v>115</v>
       </c>
       <c r="K41">
         <v>15.394938837716396</v>
       </c>
-    </row>
-    <row r="42" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L41">
+        <v>15.544809336290456</v>
+      </c>
+      <c r="M41" cm="1">
+        <f t="array" ref="M41">_xll.OPTION.BLACK.PUT_IMPLIED(f, K41, J41)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N41" cm="1">
+        <f t="array" ref="N41">_xll.OPTION.BLACK.PUT_IMPLIED(f, L41,J41)</f>
+        <v>0.10861339727042094</v>
+      </c>
+    </row>
+    <row r="42" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J42">
         <v>116</v>
       </c>
       <c r="K42">
         <v>16.326893309710854</v>
       </c>
-    </row>
-    <row r="43" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L42">
+        <v>16.458116822723056</v>
+      </c>
+      <c r="M42" cm="1">
+        <f t="array" ref="M42">_xll.OPTION.BLACK.PUT_IMPLIED(f, K42, J42)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N42" cm="1">
+        <f t="array" ref="N42">_xll.OPTION.BLACK.PUT_IMPLIED(f, L42,J42)</f>
+        <v>0.10843538591175529</v>
+      </c>
+    </row>
+    <row r="43" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J43">
         <v>117</v>
       </c>
       <c r="K43">
         <v>17.269460583629098</v>
       </c>
-    </row>
-    <row r="44" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L43">
+        <v>17.371424309155657</v>
+      </c>
+      <c r="M43" cm="1">
+        <f t="array" ref="M43">_xll.OPTION.BLACK.PUT_IMPLIED(f, K43, J43)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N43" cm="1">
+        <f t="array" ref="N43">_xll.OPTION.BLACK.PUT_IMPLIED(f, L43,J43)</f>
+        <v>0.10744257858758272</v>
+      </c>
+    </row>
+    <row r="44" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J44">
         <v>118</v>
       </c>
       <c r="K44">
         <v>18.221219204170339</v>
       </c>
-    </row>
-    <row r="45" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L44">
+        <v>18.303148905549108</v>
+      </c>
+      <c r="M44" cm="1">
+        <f t="array" ref="M44">_xll.OPTION.BLACK.PUT_IMPLIED(f, K44, J44)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N44" cm="1">
+        <f t="array" ref="N44">_xll.OPTION.BLACK.PUT_IMPLIED(f, L44,J44)</f>
+        <v>0.10681659237423599</v>
+      </c>
+    </row>
+    <row r="45" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J45">
         <v>119</v>
       </c>
       <c r="K45">
         <v>19.180890108309015</v>
       </c>
-    </row>
-    <row r="46" spans="10:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L45">
+        <v>19.271006242468232</v>
+      </c>
+      <c r="M45" cm="1">
+        <f t="array" ref="M45">_xll.OPTION.BLACK.PUT_IMPLIED(f, K45, J45)</f>
+        <v>0.1</v>
+      </c>
+      <c r="N45" cm="1">
+        <f t="array" ref="N45">_xll.OPTION.BLACK.PUT_IMPLIED(f, L45,J45)</f>
+        <v>0.10835965820573557</v>
+      </c>
+    </row>
+    <row r="46" spans="10:14" x14ac:dyDescent="0.55000000000000004">
       <c r="J46">
         <v>120</v>
       </c>
       <c r="K46">
         <v>20.14733226325697</v>
       </c>
+      <c r="L46">
+        <v>20.23886357938737</v>
+      </c>
+      <c r="M46" cm="1">
+        <f t="array" ref="M46">_xll.OPTION.BLACK.PUT_IMPLIED(f, K46, J46)</f>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="N46" cm="1">
+        <f t="array" ref="N46">_xll.OPTION.BLACK.PUT_IMPLIED(f, L46,J46)</f>
+        <v>0.10953414985532098</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/xlsx/final.xlsx
+++ b/xlsx/final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gauravg\xll_ml\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77F3E93-5FB9-431B-914A-41C05EA148E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BED8BC3-1529-4D72-B930-0781A52DB0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22875" windowHeight="13650" xr2:uid="{9BE03A92-AE89-48A8-9E12-797A60FC8C99}"/>
   </bookViews>
@@ -147,7 +147,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>n</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>strike</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>variance</t>
   </si>
 </sst>
 </file>
@@ -235,7 +241,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -246,6 +252,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Handle" xfId="1" xr:uid="{EDA68434-B044-46B3-A24D-88082F2D5A02}"/>
@@ -384,7 +391,7 @@
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="6.5247594050743651E-2"/>
-          <c:y val="0.17171296296296298"/>
+          <c:y val="0.29671296296296296"/>
           <c:w val="0.88949759405074369"/>
           <c:h val="0.6153546952464275"/>
         </c:manualLayout>
@@ -1650,14 +1657,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>292894</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>52388</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>200024</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>588169</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>52388</xdr:rowOff>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2364,6 +2371,13 @@
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="4">
+        <f>SUMPRODUCT(F3:F13, C5:C15)</f>
+        <v>2.211772431870429E-17</v>
+      </c>
       <c r="J16">
         <v>90</v>
       </c>
@@ -2377,7 +2391,14 @@
         <v>3.1622776601683795</v>
       </c>
     </row>
-    <row r="17" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="7:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="G17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" cm="1">
+        <f t="array" ref="H17">SUMPRODUCT(F3:F13*F3:F13,C5:C15)</f>
+        <v>1</v>
+      </c>
       <c r="J17">
         <v>91</v>
       </c>
@@ -2388,7 +2409,7 @@
         <v>0.92351232068490319</v>
       </c>
     </row>
-    <row r="18" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J18">
         <v>92</v>
       </c>
@@ -2399,7 +2420,7 @@
         <v>1.0953873206849032</v>
       </c>
     </row>
-    <row r="19" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J19">
         <v>93</v>
       </c>
@@ -2410,7 +2431,7 @@
         <v>1.2672623206849032</v>
       </c>
     </row>
-    <row r="20" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J20">
         <v>94</v>
       </c>
@@ -2421,7 +2442,7 @@
         <v>1.561530627262492</v>
       </c>
     </row>
-    <row r="21" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J21">
         <v>95</v>
       </c>
@@ -2432,7 +2453,7 @@
         <v>1.938483752262492</v>
       </c>
     </row>
-    <row r="22" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J22">
         <v>96</v>
       </c>
@@ -2443,7 +2464,7 @@
         <v>2.315436877262492</v>
       </c>
     </row>
-    <row r="23" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J23">
         <v>97</v>
       </c>
@@ -2454,7 +2475,7 @@
         <v>2.692390002262492</v>
       </c>
     </row>
-    <row r="24" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J24">
         <v>98</v>
       </c>
@@ -2465,7 +2486,7 @@
         <v>3.069343127262492</v>
       </c>
     </row>
-    <row r="25" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J25">
         <v>99</v>
       </c>
@@ -2476,7 +2497,7 @@
         <v>3.446296252262492</v>
       </c>
     </row>
-    <row r="26" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J26">
         <v>100</v>
       </c>
@@ -2487,7 +2508,7 @@
         <v>3.9459687470320333</v>
       </c>
     </row>
-    <row r="27" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J27">
         <v>101</v>
       </c>
@@ -2498,7 +2519,7 @@
         <v>4.5690156220320333</v>
       </c>
     </row>
-    <row r="28" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J28">
         <v>102</v>
       </c>
@@ -2509,7 +2530,7 @@
         <v>5.1920624970320333</v>
       </c>
     </row>
-    <row r="29" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J29">
         <v>103</v>
       </c>
@@ -2520,7 +2541,7 @@
         <v>5.8151093720320333</v>
       </c>
     </row>
-    <row r="30" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J30">
         <v>104</v>
       </c>
@@ -2531,7 +2552,7 @@
         <v>6.4381562470320333</v>
       </c>
     </row>
-    <row r="31" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J31">
         <v>105</v>
       </c>
@@ -2542,7 +2563,7 @@
         <v>7.0612031220320333</v>
       </c>
     </row>
-    <row r="32" spans="10:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="7:12" x14ac:dyDescent="0.55000000000000004">
       <c r="J32">
         <v>106</v>
       </c>
